--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -28,6 +28,8 @@
     <sheet name="Conflicts Log" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Sources" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="NY Home Verified" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="IL Auto Verified" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="IL Home Verified" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -697,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -719,7 +721,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida and New York auto; Texas, Florida and New York home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York and Illinois auto; Texas, Florida, New York and Illinois home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1269,277 +1271,339 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>All tabs</t>
-        </is>
-      </c>
-      <c r="B32" s="31">
-        <f>SUM(B17:B31)</f>
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>IL Auto Verified</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
+        <f>COUNTIF('IL Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C32" s="31">
-        <f>SUM(C17:C31)</f>
+      <c r="C32" s="28">
+        <f>COUNTIF('IL Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D32" s="31">
-        <f>SUM(D17:D31)</f>
+      <c r="D32" s="28">
+        <f>COUNTIF('IL Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E32" s="31">
-        <f>SUM(E17:E31)</f>
+      <c r="E32" s="28">
+        <f>COUNTIF('IL Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F32" s="31">
-        <f>SUM(F17:F31)</f>
+      <c r="F32" s="28">
+        <f>SUM(B32:E32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="29"/>
+    <row r="33" ht="15" customHeight="1" s="29">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>IL Home Verified</t>
+        </is>
+      </c>
+      <c r="B33" s="28">
+        <f>COUNTIF('IL Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C33" s="28">
+        <f>COUNTIF('IL Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>COUNTIF('IL Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>COUNTIF('IL Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>SUM(B33:E33)</f>
+        <v/>
+      </c>
+    </row>
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="31" t="inlineStr">
         <is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>SUM(B17:B33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="29"/>
+    <row r="36" ht="15" customHeight="1" s="29">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
           <t>Tabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="29">
-      <c r="A35" s="39" t="inlineStr">
-        <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="29">
-      <c r="A36" s="39" t="inlineStr">
-        <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B37" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B38" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B39" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B40" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B41" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B42" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
+          <t>Refresh Schedule</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>Conflicts Log</t>
+        </is>
+      </c>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>Where sources disagree and what to verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="28" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>NY Home Verified</t>
         </is>
       </c>
-      <c r="B55" s="28" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>IL Auto Verified</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>IL Home Verified</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="28" min="1" max="1"/>
@@ -2589,6 +2653,59 @@
       <c r="N15" s="28" t="inlineStr">
         <is>
           <t>Home credit-use rule only; NY auto credit-use rule not yet researched (left blank).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Credit: How Insurers Use It</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/credit.html</t>
+        </is>
+      </c>
+      <c r="I16" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="M16" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>215 ILCS 157 (Use of Credit Information in Personal Insurance Act) applies identically to auto and home.</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -15494,6 +15611,156 @@
         </is>
       </c>
       <c r="E99" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="B100" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="D100" s="28" t="inlineStr">
+        <is>
+          <t>IDOI consumer guide page.</t>
+        </is>
+      </c>
+      <c r="E100" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Credit: How Insurers Use It</t>
+        </is>
+      </c>
+      <c r="B101" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/credit.html</t>
+        </is>
+      </c>
+      <c r="D101" s="28" t="inlineStr">
+        <is>
+          <t>IDOI consumer guide page; cites the Use of Credit Information in Personal Insurance Act (215 ILCS 157) and FACT Act.</t>
+        </is>
+      </c>
+      <c r="E101" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="B102" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C102" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="D102" s="28" t="inlineStr">
+        <is>
+          <t>IDOI consumer guide page.</t>
+        </is>
+      </c>
+      <c r="E102" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="B103" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="D103" s="28" t="inlineStr">
+        <is>
+          <t>IDOI consumer guide page; no specific statute citation given.</t>
+        </is>
+      </c>
+      <c r="E103" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Important Insurance Information</t>
+        </is>
+      </c>
+      <c r="B104" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/important-insurance-information.html</t>
+        </is>
+      </c>
+      <c r="D104" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association's own site (carrier-equivalent published terms).</t>
+        </is>
+      </c>
+      <c r="E104" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Consumers</t>
+        </is>
+      </c>
+      <c r="B105" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/consumers.html</t>
+        </is>
+      </c>
+      <c r="D105" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association's own site; explicitly disclaims that the policy and Illinois Insurance Code control over the website.</t>
+        </is>
+      </c>
+      <c r="E105" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -16680,32 +16947,32 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Discounts</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Required hurricane-mitigation discount</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Insurers must provide discounts for hurricane-resistant shutters and hurricane-resistant windows and doors</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>DFS consumer guide (Ways to Save on Homeowners Insurance)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>NY Dept of Financial Services - Ways to Save on Homeowners Insurance</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>https://www.dfs.ny.gov/system/files/documents/2026/02/Ways-to-Save-Homeowners-Insurance.pdf</t>
         </is>
@@ -16713,17 +16980,1764 @@
       <c r="G21" s="48" t="n">
         <v>46296</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="28" t="inlineStr">
         <is>
           <t>Regulator-published</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K21" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$20,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist bodily injury</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Required by law; minimum limits of $25,000 per person and $50,000 per accident, the same as the liability minimums</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Underinsured motorist (UIM)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Mandatory when the policyholder purchases higher uninsured-motorist limits; pays the difference between the UIM limit and an at-fault driver's insufficient liability coverage</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist property damage (UMPD)</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Optional; the company must offer this coverage with a maximum $250 deductible</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Physical damage (collision/comprehensive)</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Not required by state law, but lenders typically require it for financed vehicles; deductibles range from $0 to $1,000</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Medical payments</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Optional coverage available for medical and funeral expenses (Illinois does not require PIP/no-fault coverage)</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Notable discounts available</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Good student (B average or better), defensive driver (age 55+), multiple vehicles, safety devices, low mileage, and bundled policies</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto shopping guide</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Credit-based insurance score restrictions</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>215 ILCS 157 (Use of Credit Information in Personal Insurance Act)</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Credit: How Insurers Use It</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/credit.html</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Dwelling coverage</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Covers damage to the house; the face amount of the policy (for example $100,000) is the most you will receive if the house is totally destroyed</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Other structures</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Covers damage to other structures such as a detached garage, work shed, or fencing</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Personal property</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Covers damage to or loss of household contents and other personal belongings used, owned, or worn by you and your family</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Additional living expense</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Covers necessary living costs when the home cannot be occupied due to a covered loss</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Comprehensive personal liability</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Protects against claims arising from accidents to others on property you own or rent</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Medical expense coverage</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Limited to an amount per person and per accident for injuries occurring on your premises</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost vs actual cash value</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost rebuilds without a depreciation deduction; actual cash value applies depreciation; it is recommended to insure the home for at least 80% of its replacement value</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Flood and earthquake exclusion</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Flood and earthquake damage are explicitly not covered by standard homeowners policies</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Deductibles</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Typical deductible range</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Typically $100 to $250 or more</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Available discounts</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Insurers may offer discounts for bundling auto coverage, home security systems, or disaster-proofing measures</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowner/renter shopping tips</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Homeowner/Renter Shopping Tips and Information</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/shopping-tips-and-information.html</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>The Illinois FAIR Plan Association's mission is to make basic property insurance available to qualified applicants who have not been able to obtain property insurance; it offers Dwelling Property and Homeowners policies</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan - Important Insurance Information</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Important Insurance Information</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/important-insurance-information.html</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>What it covers</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Fire, lightning, wind, hail, explosion, smoke, vehicles, aircraft, and vandalism and malicious mischief; homeowners policies additionally provide burglary, theft and personal liability coverage</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan - Consumers page</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Consumers</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/consumers.html</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L13" s="28" t="inlineStr">
+        <is>
+          <t>Unlike California's FAIR Plan or New York's NYPIUA, Illinois's FAIR Plan homeowners form includes theft and liability coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Earthquake endorsement</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Earthquake coverage is available, upon request, as an endorsement to the Dwelling Property and Homeowners policy, with a standard 5% deductible; not available for Commercial Property</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan - Consumers page</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Consumers</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/consumers.html</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>The applicant must be unable to buy insurance through the standard market for reasons beyond their control, and the property must meet reasonable safety standards verified by a representative inspection</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan - Consumers page</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Illinois FAIR Plan Association - Consumers</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>https://www.illinoisfairplan.com/consumers.html</t>
+        </is>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K15" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Notice period for policies active less than 5 years</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>At least 30 days before the nonrenewal date</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>IDOI non-renewal guide</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K16" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Prohibited reasons</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>A company cannot nonrenew based on the age or location of the property, or the age, gender, race, color, ancestry, marital status, or occupation of the occupants, or solely on credit report information</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>IDOI non-renewal guide</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K17" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Hate crime protection</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Nonrenewal is prohibited solely on the basis that one or more claims resulted from a hate crime, if documented by a police report (effective January 1, 2003)</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>IDOI non-renewal guide</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K18" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Notice content requirements</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>The notice must explain the specific reason(s) for nonrenewal with a factual basis (not vague terms), and must inform the policyholder of appeal rights and FAIR Plan eligibility</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>IDOI non-renewal guide</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K19" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Notice period for policies active 5 or more years</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>A 30-day notice is allowed only for two reasons (the policy was obtained through misleading or incorrect information, or a significant change has occurred creating a measurably greater chance of loss); a 60-day notice is required for almost any other reason; the same prohibitions on age, location, occupant demographics, and credit-based denial still apply</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>IDOI non-renewal guide</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - If Your Homeowners Insurance Policy is Non-Renewed</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/homeownerrenter/if-your-homeowners-insurance-policy-is-non-renewed.html</t>
+        </is>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I20" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K20" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Credit-based insurance score restrictions</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>215 ILCS 157 (Use of Credit Information in Personal Insurance Act)</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Credit: How Insurers Use It</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/credit.html</t>
+        </is>
+      </c>
+      <c r="G21" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="I21" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>Primary source</t>
         </is>
@@ -25161,17 +27175,39 @@
           <t>Illinois</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
+      <c r="B15" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" s="41" t="n">
+        <v>20</v>
+      </c>
       <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
-      <c r="G15" s="41" t="n"/>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>Medical payments optional (no PIP/no-fault requirement)</t>
+        </is>
+      </c>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>UM bodily injury required at $25,000/$50,000 (same as liability minimums); UIM mandatory when buying higher UM limits; UMPD optional, insurer must offer with a max $250 deductible</t>
+        </is>
+      </c>
       <c r="H15" s="41" t="n"/>
-      <c r="I15" s="41" t="n"/>
-      <c r="J15" s="42" t="n"/>
+      <c r="I15" s="41" t="inlineStr">
+        <is>
+          <t>Illinois Dept of Insurance - Auto Insurance Shopping Guide</t>
+        </is>
+      </c>
+      <c r="J15" s="42" t="inlineStr">
+        <is>
+          <t>https://idoi.illinois.gov/consumers/consumerinsurance/auto-insurance-shopping-guide.html</t>
+        </is>
+      </c>
       <c r="K15" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L15" s="41" t="inlineStr">
         <is>
@@ -25180,16 +27216,16 @@
       </c>
       <c r="M15" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N15" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O15" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P15" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -30,6 +30,8 @@
     <sheet name="NY Home Verified" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="IL Auto Verified" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="IL Home Verified" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="PA Auto Verified" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="PA Home Verified" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -699,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -721,7 +723,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York and Illinois auto; Texas, Florida, New York and Illinois home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois and Pennsylvania auto; Texas, Florida, New York, Illinois and Pennsylvania home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1327,20 +1329,82 @@
     <row r="34" ht="15" customHeight="1" s="29">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B34" s="31">
-        <f>SUM(B17:B33)</f>
+        <f>COUNTIF('PA Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="29"/>
+      <c r="C34" s="28">
+        <f>COUNTIF('PA Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D34" s="28">
+        <f>COUNTIF('PA Auto Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>COUNTIF('PA Auto Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F34" s="28">
+        <f>SUM(B34:E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="29">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>PA Home Verified</t>
+        </is>
+      </c>
+      <c r="B35" s="28">
+        <f>COUNTIF('PA Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C35" s="28">
+        <f>COUNTIF('PA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>COUNTIF('PA Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>COUNTIF('PA Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>SUM(B35:E35)</f>
+        <v/>
+      </c>
+    </row>
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>Tabs</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B36" s="28">
+        <f>SUM(B17:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="28">
+        <f>SUM(C17:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="28">
+        <f>SUM(D17:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>SUM(E17:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="28">
+        <f>SUM(F17:F35)</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
@@ -1571,6 +1635,13 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tabs (additional entries below)</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
@@ -1607,8 +1678,32 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PA Home Verified</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B3:F3"/>
@@ -1623,7 +1718,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
@@ -1632,10 +1726,8 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2657,27 +2749,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>Credit-based insurance scores used for auto and home insurance may not consider race, color, national origin, religion, gender, marital status, age, income, occupation or employment history, location of residence, any interest rate being charged, child/family support obligations or rental agreements, or certain credit inquiries (account review, employment, promotional) or credit counseling participation; insurers cannot base renewal rates solely on credit information; an insurer must use a credit report or score obtained within 90 days of writing or renewing a policy to take an adverse action; consumers may request premium reconsideration after an extraordinary life circumstance such as a catastrophic event, job loss, or serious illness</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Illinois Dept of Insurance - Credit: How Insurers Use It</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>https://idoi.illinois.gov/consumers/consumerinsurance/credit.html</t>
         </is>
@@ -2685,17 +2777,17 @@
       <c r="I16" s="48" t="n">
         <v>46296</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="28" t="inlineStr">
         <is>
           <t>Illinois</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="28" t="inlineStr">
         <is>
           <t>Regulator-published</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="28" t="inlineStr">
         <is>
           <t>Primary source</t>
         </is>
@@ -2703,7 +2795,7 @@
       <c r="M16" s="48" t="n">
         <v>46296</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>215 ILCS 157 (Use of Credit Information in Personal Insurance Act) applies identically to auto and home.</t>
         </is>
@@ -13187,7 +13279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -15761,6 +15853,56 @@
         </is>
       </c>
       <c r="E105" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="B106" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C106" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="D106" s="28" t="inlineStr">
+        <is>
+          <t>Official PA Insurance Department consumer PDF guide (Rev. 10/2016 v3).</t>
+        </is>
+      </c>
+      <c r="E106" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="B107" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="D107" s="28" t="inlineStr">
+        <is>
+          <t>Official PA Insurance Department consumer PDF guide (Rev. 4/2017).</t>
+        </is>
+      </c>
+      <c r="E107" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -18751,6 +18893,2134 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$15,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$5,000; some companies offer a combined single limit of $35,000 which meets both the bodily injury and property damage minimums</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Medical Benefits (required)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Required coverage; pays medical bills for the policyholder and others covered by the policy regardless of fault; minimum limit is $5,000; higher limits available</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Full tort / limited tort</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Default and effect</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>If a policyholder does not specially elect limited tort, they are deemed to have elected full tort (unrestricted right to sue). Limited tort offers significant premium savings but restricts recovery for damages such as pain and suffering unless the injury meets one of the exceptions in the law</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist (UM)</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Optional; applies to the policyholder, household relatives, and passengers if injured by an at-fault uninsured motorist or hit-and-run driver; does not cover property damage</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Underinsured motorist (UIM)</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Optional; applies to the policyholder, household relatives, and passengers if injured by an at-fault motorist without enough insurance to pay the claim; does not cover property damage</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Stacking of UM/UIM</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>By law, stacked UM/UIM coverage (multiplying the limit by the number of covered vehicles, or combining coverage from more than one policy) applies unless the policyholder rejects it; rejecting stacked coverage lowers the premium</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Collision deductible default</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>By Pennsylvania law, the insurance company applies a $500 collision deductible unless the policyholder requests a lower amount</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Extraordinary Medical Benefits</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Optional; pays medical and rehabilitation expenses that exceed $100,000, up to a maximum limit of $1.1 million</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Mature driver discount (required)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Mandated by law: insurers must provide at least a 5% premium discount for each vehicle on a policy where all named insureds are 55 or older and have completed a PennDOT-approved driver improvement course; the course must be retaken every 3 years, and the discount can be lost if the insured has a chargeable accident, a moving-violation conviction, or a DUI conviction/ARD within 3 years of completion</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Rate-setting anti-discrimination</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>By law, insurance companies are prohibited from charging different rates based on an applicant's race, religion, national origin, and gender</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Credit history</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Some companies may use credit history when determining a premium; companies cannot use credit history to increase the rate at renewal</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation for non-payment</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania insurance law does not require companies to extend a grace period for premium payments; the company can cancel the policy if the premium is not received by the due date</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K15" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal timing</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>An insurance company can only non-renew a policy on the annual anniversary of when it was initially written, even if the policy term itself is less than 12 months</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K16" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Appeal window (auto)</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>To preserve appeal rights after a cancellation or non-renewal notice, a statement disagreeing with the action must be received by the Pennsylvania Insurance Department within 30 days of the company's mailing of the notice</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K17" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Claim handling timelines</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>An insurer has 10 working days to acknowledge receipt of a claim (unless payment is made within that time); 15 working days after receiving proofs of loss to accept or deny the claim or explain why more time is needed; and must complete its investigation within 30 days unless that is not reasonably possible, in which case it must explain the delay every 45 days thereafter</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K18" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>State-backed plan</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Assigned Risk Plan</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>All insurance companies writing automobile insurance in Pennsylvania are required to participate in the Assigned Risk Plan, which offers coverage to drivers unable to obtain it on their own; applicants are assigned to companies in proportion to the amount of business each writes in the state</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>IDOI auto insurance guide</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
+        </is>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K19" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Homeowners insurance is not mandatory</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Homeowners insurance is not mandatory in Pennsylvania, but most banks or lenders will require coverage for at least the amount of the mortgage</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Dwelling coverage</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Pays for damage to the house and structures attached to it, including fixtures such as plumbing, electrical wiring, heating, and permanently installed cooling systems</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Other structures</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Typically limited to 10% of the dwelling coverage limit; covers structures not attached to the dwelling such as detached garages, sheds, fences, and guest houses</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Personal property</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Typically provided at a percentage of the dwelling coverage limit; personal property away from the home (for business or vacation) is typically insured for 10% of the personal property coverage or $1,000, whichever is greater, unless a higher limit is requested</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Loss of use</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Typical coverage for loss of use (additional living expenses while the home is being repaired) is 20% of the dwelling coverage limit</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Personal liability</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Most policies offer $100,000, with higher limits available for an additional cost; covers the policyholder, household relatives, residents under 21, and students under 24 enrolled full-time at school (with certain exceptions)</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Medical payments to others</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Basic amounts of coverage are usually $1,000 per person; higher limits may be available for an additional cost</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost vs actual cash value</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost is the amount to rebuild or repair without deducting for depreciation; actual cash value is replacement cost minus depreciation. A good rule of thumb is to insure the home for at least 80% of its replacement value; if coverage drops below that, the company may reduce the amount paid on a claim</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Policy forms</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>The Broad Form (Form 2) covers only perils specifically named in the policy. The Special Form (Form 3) instead specifies which perils are not covered, providing more coverage. The Comprehensive Form (Form 5) extends open-peril coverage to personal property as well. The Modified Coverage Form (Form 8) provides 'functional replacement cost' for older homes. The Contents Broad Form (Form 4) is for renters, and the Unit-Owners Form (Form 6) is for condominium owners</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Common exclusions</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Common exclusions include (but are not limited to) earthquake, collapse, flood, mold/fungus/wet rot, wear and tear, mechanical breakdown, and sinkhole or earth movement; separate coverage can typically be purchased for some of these</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania's 'Fair Plan' guarantees the availability of basic fire insurance for a home when a homeowner cannot find a company to insure it</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L12" s="28" t="inlineStr">
+        <is>
+          <t>Official site: www.pafairplan.com or 1-800-462-4972.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Flood insurance</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>A typical homeowners or renters policy does not cover flood damage. National Flood Insurance Program (NFIP) policies have a 30-day waiting period before they take effect. Private flood insurance, including through surplus lines insurers, is also available</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Sinkhole and earth movement</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Damage from sinkholes or earth movement is typically not covered unless specifically requested and purchased at additional cost; separate mine subsidence coverage is available through the PA Department of Environmental Protection for communities above old mines</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Credit history (general guidance)</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>The guide, citing NAIC consumer education, notes that in many states insurers use credit history as a factor in deciding whether to offer coverage and what to charge; the insurance agent may ask for a Social Security number to access a credit report</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide (citing NAIC)</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K15" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L15" s="28" t="inlineStr">
+        <is>
+          <t>Framed as general multi-state guidance in the PA guide, not a PA-specific statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Underwriting / free-look period</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>An insurance company has 60 days to underwrite and investigate an application and may refuse or cancel coverage within that period for various reasons, but not because of age, marital status, occupation, or any other unfairly discriminatory reason</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K16" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>No cancellation for claims or loss history</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania law does not allow an insurance company to terminate a homeowner's insurance policy for 'claims' or 'loss history'</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K17" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation for non-payment</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania insurance law does not require companies to extend a grace period for premium payments; the company can cancel the policy if the premium is not paid on time</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K18" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Appeal window (home)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>To preserve appeal rights, a statement disagreeing with a cancellation or non-renewal action must be received by the Pennsylvania Insurance Department within 10 days of the homeowner's receipt of the notice</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K19" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L19" s="28" t="inlineStr">
+        <is>
+          <t>Shorter than, and measured differently from, the 30-day auto appeal window (which runs from the company's mailing date, not the consumer's receipt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Home-improvement contractor registration</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>Home-improvement contractors doing more than $5,000 of business per year in Pennsylvania must register with the Attorney General's Bureau of Consumer Protection; homeowners can verify a contractor's registration number before hiring</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>IDOI homeowners insurance guide</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania Insurance Department - Homeowners Insurance Guide</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/coverage/homeowners/documents/homeowners%20insurance%20guide.pdf</t>
+        </is>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I20" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K20" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -28413,41 +30683,47 @@
           <t>Pennsylvania</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
-        <is>
-          <t>Not captured</t>
-        </is>
-      </c>
-      <c r="C40" s="41" t="inlineStr">
-        <is>
-          <t>Not captured</t>
-        </is>
-      </c>
-      <c r="D40" s="41" t="inlineStr">
-        <is>
-          <t>Not captured</t>
-        </is>
-      </c>
-      <c r="E40" s="41" t="n"/>
+      <c r="B40" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="C40" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="41" t="inlineStr">
+        <is>
+          <t>Choice no-fault (full tort / limited tort election)</t>
+        </is>
+      </c>
       <c r="F40" s="41" t="inlineStr">
         <is>
-          <t>MedPay required (per Beach Insurance)</t>
-        </is>
-      </c>
-      <c r="G40" s="41" t="n"/>
-      <c r="H40" s="41" t="n"/>
+          <t>Medical Benefits required, minimum $5,000, pays regardless of fault</t>
+        </is>
+      </c>
+      <c r="G40" s="41" t="inlineStr">
+        <is>
+          <t>UM/UIM optional; stacking applies by law unless rejected</t>
+        </is>
+      </c>
+      <c r="H40" s="41" t="inlineStr">
+        <is>
+          <t>Combined single limit option of $35,000 meets both BI and PD minimums</t>
+        </is>
+      </c>
       <c r="I40" s="41" t="inlineStr">
         <is>
-          <t>Beach Insurance LLC - State minimums 2026</t>
+          <t>Pennsylvania Insurance Department - Automobile Insurance Guide</t>
         </is>
       </c>
       <c r="J40" s="42" t="inlineStr">
         <is>
-          <t>https://beachinsurancellc.com/blog/state-minimum-car-insurance-requirements-for-2026-your-essential-guide</t>
+          <t>https://www.pa.gov/content/dam/copapwp-pagov/en/insurance/documents/consumer-help-center/learn-about-insurance/auto-insurance-guide.pdf</t>
         </is>
       </c>
       <c r="K40" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L40" s="41" t="inlineStr">
         <is>
@@ -28456,16 +30732,16 @@
       </c>
       <c r="M40" s="41" t="inlineStr">
         <is>
-          <t>Reference data (secondary source)</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N40" s="45" t="inlineStr">
         <is>
-          <t>Secondary - unverified</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O40" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P40" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -32,6 +32,8 @@
     <sheet name="IL Home Verified" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="PA Auto Verified" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="PA Home Verified" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="GA Auto Verified" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="GA Home Verified" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -701,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -723,7 +725,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois and Pennsylvania auto; Texas, Florida, New York, Illinois and Pennsylvania home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania and Georgia auto; Texas, Florida, New York, Illinois, Pennsylvania and Georgia home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1383,322 +1385,401 @@
     <row r="36" ht="15" customHeight="1" s="29">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B36" s="28">
-        <f>SUM(B17:B35)</f>
+        <f>COUNTIF('GA Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
       <c r="C36" s="28">
-        <f>SUM(C17:C35)</f>
+        <f>COUNTIF('GA Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
       <c r="D36" s="28">
-        <f>SUM(D17:D35)</f>
+        <f>COUNTIF('GA Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
       <c r="E36" s="28">
-        <f>SUM(E17:E35)</f>
+        <f>COUNTIF('GA Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
       <c r="F36" s="28">
-        <f>SUM(F17:F35)</f>
+        <f>SUM(B36:E36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="29">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>GA Home Verified</t>
+        </is>
+      </c>
+      <c r="B37" s="39">
+        <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>SUM(B37:E37)</f>
+        <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B38" s="39">
+        <f>SUM(B17:B37)</f>
+        <v/>
+      </c>
+      <c r="C38">
+        <f>SUM(C17:C37)</f>
+        <v/>
+      </c>
+      <c r="D38">
+        <f>SUM(D17:D37)</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>SUM(E17:E37)</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>SUM(F17:F37)</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B39" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B40" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B41" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B42" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Tabs (additional entries below)</t>
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>Conflicts Log</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="inlineStr">
-        <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
-        </is>
-      </c>
+          <t>Tabs (additional entries below)</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
+          <t>NY Home Verified</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>IL Auto Verified</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
           <t>IL Home Verified</t>
         </is>
       </c>
-      <c r="B59" s="28" t="inlineStr">
+      <c r="B61" s="28" t="inlineStr">
         <is>
           <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>PA Auto Verified</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>PA Home Verified</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GA Home Verified</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
@@ -1706,6 +1787,7 @@
   <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B54:F54"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B52:F52"/>
@@ -1717,9 +1799,8 @@
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B6:F6"/>
@@ -13279,7 +13360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -15903,6 +15984,56 @@
         </is>
       </c>
       <c r="E107" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="B108" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C108" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="D108" s="28" t="inlineStr">
+        <is>
+          <t>Official Georgia OCI consumer PDF guide.</t>
+        </is>
+      </c>
+      <c r="E108" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="B109" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="D109" s="28" t="inlineStr">
+        <is>
+          <t>Official Georgia OCI consumer PDF guide.</t>
+        </is>
+      </c>
+      <c r="E109" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -21021,6 +21152,1546 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide (25/50/25)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide (25/50/25)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide (25/50/25)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>What liability insurance covers</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Liability coverage pays only for damage the policyholder does to others or to the property of others; it does not cover the policyholder's own vehicle</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Collision and comprehensive</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Both optional under state law; collision covers damage to the policyholder's own car from an accident, comprehensive covers damage from causes such as fire, theft, glass breakage, vandalism, flood, falling objects, explosion, windstorm, hail, earthquake, riot, or collision with an animal; lenders commonly require both as a loan condition on financed or leased vehicles</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Medical Payments coverage</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Optional, available in varying amounts, to cover injuries to the policyholder or passengers in an auto accident</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Optional; pays the policyholder for damages from an at-fault uninsured driver just as if that driver had been covered</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Good student discount (required)</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Insurance companies are required to offer a reduction in liability, first-party medical, and collision rates for drivers who qualify as 'good students' by meeting one of: ranked in the upper 20% of their class, a 'B' average or better, a 3.0 GPA or better, or Dean's List/Honor Roll membership; other conditions may apply</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Rating factors</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Common premium factors</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Most insurance companies look at driving records, type of car, use of the vehicle, location of the vehicle, and age of the driver when setting premiums</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Quotes</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Quotes are binding once filed</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>A quote represents an offer to sell a contract subject to compatibility with the carrier's filings with the Department; an insurance company may not collect a premium for less than or more than the filed amount</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal appeal window</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>A policyholder who believes a non-renewal was unfair may request a written review before the Insurance Commissioner or a designee; the request must be made within 15 days of the non-renewal notice and must state why the non-renewal is believed unfair</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Three-year, one-claim protection</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia law states that if a policyholder has been with the same insurance company for at least three years, the company cannot non-renew the policy because of just one claim, even if the policyholder was at fault for that claim</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide (cites Georgia law)</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>State-backed plan</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Non-standard insurers</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>A 'non-standard' automobile insurance company writes coverage for drivers who have difficulty obtaining insurance through normal means; non-standard companies generally charge higher premiums</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>OCI auto guide</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What a homeowners policy covers</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>A homeowner's policy usually covers: property damage to the home and other detached buildings; contents and personal belongings; reimbursement for additional living expenses if the home is damaged and uninhabitable; and personal liability for injuries to others or damage to their property</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Common exclusions</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Most homeowners policies will not cover vehicles or vehicle stereo equipment, or losses from natural disasters such as flooding, earthquakes, or nuclear accidents; separate coverage can usually be purchased for these</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost vs actual cash value</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Most standard policies provide replacement cost coverage for the dwelling up to the policy limit, but settle contents and personal belongings at actual cash value (replacement cost minus depreciation) unless replacement-cost coverage is added for an additional charge</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>80% replacement-value guideline</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>It is generally best to insure a home at the full cost to rebuild; choosing to insure for less than 80% of the home's replacement value may mean not receiving the full value of a claim</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Contents coverage guideline</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage of a home's contents is usually recommended at an amount equal to at least half of the dwelling (structure) coverage</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Special limits on valuables</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Theft following a disaster imposes low monetary limits on items such as money, jewelry, furs, silverware, and guns unless they are specifically scheduled; higher limits may be warranted for these items</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Water damage from appliances vs. flooding</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Water damage from an overflowing washing machine or dishwasher is normally covered by a homeowner's policy, but damage from rising flood water during a storm is not</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Flood insurance availability</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>If a homeowner's local government participates in the Federal Flood Program, the homeowner can request a special flood insurance policy</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>Guide lists 800-427-4661 (the NFIP's consumer line) for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Loss of use / additional living expenses</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Many homeowners policies have provisions to pay a reasonable increase in living expenses needed to maintain the insured's normal standard of living if the home becomes uninhabitable; whether this coverage exists, and in what amount, depends on the specific policy</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Renter's insurance</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>A renter's policy covers the contents of the rented unit but does not insure the structure itself; insurance for the structure of a rental building is generally carried by the building's owner</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Safety-feature discounts</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Most insurance carriers offer discounts for home safety features such as smoke alarms; the amount of the reduction varies by company</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>The Georgia FAIR Plan is an association of Georgia-licensed insurers, authorized by the state insurance code, to maintain fair access to property insurance for homeowners who cannot obtain coverage in the standard market</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L13" s="28" t="inlineStr">
+        <is>
+          <t>Guide lists (770) 923-7431 as the Fair Plan's contact number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>What to do about a non-renewal</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>A homeowner whose policy is not being renewed should first contact the Commissioner's Consumer Services Division to find out whether the non-renewal meets statutory requirements and whether it can be rescinded</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>OCI homeowners guide</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Homeowners Insurance</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>https://ociapp.oci.ga.gov/Resources/Documents/ConsumerServices/Guide%20for%20Homeowners%20Insurance.pdf</t>
+        </is>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K14" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -29301,17 +30972,39 @@
           <t>Georgia</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
+      <c r="B12" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C12" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
-      <c r="G12" s="41" t="n"/>
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>Medical Payments optional, in varying amounts</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage optional</t>
+        </is>
+      </c>
       <c r="H12" s="41" t="n"/>
-      <c r="I12" s="41" t="n"/>
-      <c r="J12" s="42" t="n"/>
+      <c r="I12" s="41" t="inlineStr">
+        <is>
+          <t>Georgia OCI - Consumer Guide for Automobile Insurance</t>
+        </is>
+      </c>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t>https://oci.georgia.gov/document/document/guide-auto-insurance/download</t>
+        </is>
+      </c>
       <c r="K12" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L12" s="41" t="inlineStr">
         <is>
@@ -29320,16 +31013,16 @@
       </c>
       <c r="M12" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N12" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O12" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P12" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -34,6 +34,8 @@
     <sheet name="PA Home Verified" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="GA Auto Verified" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="GA Home Verified" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="NC Auto Verified" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="NC Home Verified" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -703,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -725,7 +727,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania and Georgia auto; Texas, Florida, New York, Illinois, Pennsylvania and Georgia home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1419,19 +1421,19 @@
         <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C37">
+      <c r="C37" s="28">
         <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D37">
+      <c r="D37" s="28">
         <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E37">
+      <c r="E37" s="28">
         <f>COUNTIF('GA Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F37">
+      <c r="F37" s="28">
         <f>SUM(B37:E37)</f>
         <v/>
       </c>
@@ -1439,347 +1441,425 @@
     <row r="38" ht="15" customHeight="1" s="29">
       <c r="A38" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B38" s="39">
-        <f>SUM(B17:B37)</f>
+        <f>COUNTIF('NC Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C38">
-        <f>SUM(C17:C37)</f>
+      <c r="C38" s="28">
+        <f>COUNTIF('NC Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D38">
-        <f>SUM(D17:D37)</f>
+      <c r="D38" s="28">
+        <f>COUNTIF('NC Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E38">
-        <f>SUM(E17:E37)</f>
+      <c r="E38" s="28">
+        <f>COUNTIF('NC Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F38">
-        <f>SUM(F17:F37)</f>
+      <c r="F38" s="28">
+        <f>SUM(B38:E38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="29">
       <c r="A39" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>NC Home Verified</t>
+        </is>
+      </c>
+      <c r="B39" s="39">
+        <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C39">
+        <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D39">
+        <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E39">
+        <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>SUM(B39:E39)</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B40" s="39">
+        <f>SUM(B17:B39)</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>SUM(C17:C39)</f>
+        <v/>
+      </c>
+      <c r="D40">
+        <f>SUM(D17:D39)</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>SUM(E17:E39)</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>SUM(F17:F39)</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B41" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B42" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Legal Review Checklist</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="n"/>
+          <t>Conflicts Log</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>Where sources disagree and what to verify.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
-        </is>
-      </c>
+          <t>Tabs (additional entries below)</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
+          <t>NY Home Verified</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>IL Auto Verified</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
           <t>IL Home Verified</t>
         </is>
       </c>
-      <c r="B61" s="28" t="inlineStr">
+      <c r="B63" s="28" t="inlineStr">
         <is>
           <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>PA Auto Verified</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" s="28" t="inlineStr">
         <is>
           <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>PA Home Verified</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B65" s="28" t="inlineStr">
         <is>
           <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>GA Auto Verified</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>GA Home Verified</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NC Auto Verified</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NC Home Verified</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
@@ -1790,19 +1870,19 @@
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
@@ -13360,7 +13440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16034,6 +16114,81 @@
         </is>
       </c>
       <c r="E109" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
+        </is>
+      </c>
+      <c r="B110" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
+        </is>
+      </c>
+      <c r="D110" s="28" t="inlineStr">
+        <is>
+          <t>Official NCDOI bulletin page.</t>
+        </is>
+      </c>
+      <c r="E110" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV - Vehicle Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="B111" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdot.gov/dmv/title-registration/insurance-requirements/Pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="D111" s="28" t="inlineStr">
+        <is>
+          <t>Official NCDOT DMV consumer page; cross-confirms NCDOI's numbers.</t>
+        </is>
+      </c>
+      <c r="E111" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="B112" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C112" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="D112" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plans' own administrator.</t>
+        </is>
+      </c>
+      <c r="E112" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -22692,6 +22847,847 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$50,000 (raised from $30,000 for policies issued/renewed on or after July 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI bulletin</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$100,000 (raised from $60,000 for policies issued/renewed on or after July 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI bulletin</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$50,000 (raised from $25,000 for policies issued/renewed on or after July 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI bulletin</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Underinsured motorist now required</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Underinsured motorist coverage is included in all new or renewed policies on or after July 1, 2025; previously, policies at the old minimum limits did not include it automatically</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI bulletin</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured/underinsured motorist coverage is mandated on all policies, even those exceeding the minimum liability limits</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV - Vehicle Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdot.gov/dmv/title-registration/insurance-requirements/Pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Proof of insurance (FS-1)</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Insurance companies must electronically submit a Certificate of Insurance (FS-1) to demonstrate continuous coverage; only policies from insurers licensed to do business in North Carolina are accepted, so out-of-state policies are rejected</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV - Vehicle Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdot.gov/dmv/title-registration/insurance-requirements/Pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Penalties for a lapse in coverage</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Civil penalties for a lapse range from $50 to $150 depending on prior lapse history within three years, plus a $50 restoration fee at registration renewal; license plate revocation is possible for unpaid penalties</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>NC DMV - Vehicle Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncdot.gov/dmv/title-registration/insurance-requirements/Pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>NC FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>A market of last resort created by the NC General Assembly in 1969, offering full peril commercial fire and dwelling fire coverage statewide, excluding the beach area</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>NC FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage limits</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Maximum residential building coverage of $1,000,000; personal property capped at 40% of the building coverage limit</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>NC Beach Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>The Coastal Property Insurance Pool (formerly the Beach Plan) offers commercial, homeowner, and dwelling windstorm coverage, plus homeowner and commercial fire coverage, to properties in the 18 eligible coastal counties</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>NC Beach Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage limits</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Maximum residential building coverage of $1,000,000; personal property capped at 40% of the building coverage limit; maximum commercial combined limit of $4 million</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>NC Beach Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Windstorm eligibility condition</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>The windstorm product requires an active primary coverage policy from a carrier admitted in North Carolina that has excluded windstorm coverage</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>NC FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Market of last resort</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Both the FAIR Plan and the Coastal Property Insurance Pool are a market of last resort; applicants are expected to attempt to obtain insurance in the standard market first</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>NCJUA/NCIUA (FAIR/Beach Plans administrator)</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>NC Joint Underwriting Association / Insurance Underwriting Association (FAIR/Beach Plans)</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.ncjua-nciua.org/html/svcs_cov.htm</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -32163,24 +33159,28 @@
       </c>
       <c r="E35" s="41" t="n"/>
       <c r="F35" s="41" t="n"/>
-      <c r="G35" s="41" t="n"/>
+      <c r="G35" s="41" t="inlineStr">
+        <is>
+          <t>UM/UIM mandated on all policies</t>
+        </is>
+      </c>
       <c r="H35" s="41" t="inlineStr">
         <is>
-          <t>Raised in 2025 per source</t>
+          <t>Raised from 30/60/25, effective for policies issued/renewed on or after July 1, 2025</t>
         </is>
       </c>
       <c r="I35" s="41" t="inlineStr">
         <is>
-          <t>CarInsurance.com - Minimum liability by state (Apr 2026)</t>
+          <t>NCDOI - Changes to the Rating of Automobile Insurance Policies</t>
         </is>
       </c>
       <c r="J35" s="42" t="inlineStr">
         <is>
-          <t>https://www.carinsurance.com/Articles/minimum-liability-car-insurance-requirements-by-state.aspx</t>
+          <t>https://www.ncdoi.gov/changes-rating-automobile-insurance-policies-effective-july-1-2025</t>
         </is>
       </c>
       <c r="K35" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L35" s="41" t="inlineStr">
         <is>
@@ -32189,16 +33189,16 @@
       </c>
       <c r="M35" s="41" t="inlineStr">
         <is>
-          <t>Reference data (secondary source)</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N35" s="45" t="inlineStr">
         <is>
-          <t>Secondary - unverified</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O35" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P35" s="41" t="n"/>
     </row>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -36,6 +36,8 @@
     <sheet name="GA Home Verified" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="NC Auto Verified" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="NC Home Verified" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="NJ Auto Verified" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="NJ Home Verified" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -705,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -727,7 +729,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina and New Jersey auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina and New Jersey home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1475,19 +1477,19 @@
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C39">
+      <c r="C39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D39">
+      <c r="D39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E39">
+      <c r="E39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F39">
+      <c r="F39" s="28">
         <f>SUM(B39:E39)</f>
         <v/>
       </c>
@@ -1495,282 +1497,316 @@
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B40" s="39">
-        <f>SUM(B17:B39)</f>
+        <f>COUNTIF('NJ Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C40">
-        <f>SUM(C17:C39)</f>
+      <c r="C40" s="28">
+        <f>COUNTIF('NJ Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D40">
-        <f>SUM(D17:D39)</f>
+      <c r="D40" s="28">
+        <f>COUNTIF('NJ Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E40">
-        <f>SUM(E17:E39)</f>
+      <c r="E40" s="28">
+        <f>COUNTIF('NJ Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F40">
-        <f>SUM(F17:F39)</f>
+      <c r="F40" s="28">
+        <f>SUM(B40:E40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>NJ Home Verified</t>
+        </is>
+      </c>
+      <c r="B41" s="39">
+        <f>COUNTIF('NJ Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>COUNTIF('NJ Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D41">
+        <f>COUNTIF('NJ Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>COUNTIF('NJ Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>SUM(B41:E41)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B42" s="39">
+        <f>SUM(B17:B41)</f>
+        <v/>
+      </c>
+      <c r="C42">
+        <f>SUM(C17:C41)</f>
+        <v/>
+      </c>
+      <c r="D42">
+        <f>SUM(D17:D41)</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>SUM(E17:E41)</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>SUM(F17:F41)</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="n"/>
+          <t>Conflicts Log</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Where sources disagree and what to verify.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
@@ -1782,84 +1818,132 @@
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
+          <t>IL Home Verified</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>PA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
           <t>PA Home Verified</t>
         </is>
       </c>
-      <c r="B65" s="28" t="inlineStr">
+      <c r="B67" s="28" t="inlineStr">
         <is>
           <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>GA Auto Verified</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" s="28" t="inlineStr">
         <is>
           <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>GA Home Verified</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" s="28" t="inlineStr">
         <is>
           <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>NC Auto Verified</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>NC Home Verified</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NJ Auto Verified</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NJ Home Verified</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
@@ -1871,13 +1955,14 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B10:F10"/>
@@ -1888,7 +1973,6 @@
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10960,10 +11044,14 @@
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="41" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>Not actually conflicting. NJDOBI Bulletin 25-06 confirms Standard Policy minimums rose to 35/70/25 effective Jan 1, 2026 (P.L.2022, c.87); footnote 1 of the same bulletin confirms the Act does not apply to the Basic Policy (N.J.S.A. 39:6A-3.1), which remains PIP $15,000/PD $5,000/optional BI $10,000. The "Coverage Criteria" document was describing the still-valid Basic Policy, not an outdated Standard Policy figure.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="29">
       <c r="A5" s="41" t="inlineStr">
@@ -13440,7 +13528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16189,6 +16277,81 @@
         </is>
       </c>
       <c r="E112" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="28" t="inlineStr">
+        <is>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
+        </is>
+      </c>
+      <c r="B113" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
+        </is>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>Official NJDOBI bulletin PDF, read directly.</t>
+        </is>
+      </c>
+      <c r="E113" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="28" t="inlineStr">
+        <is>
+          <t>P.L.1998, c.21 (AICRA) - N.J.S.A. 39:6A-3.1, Basic Automobile Insurance Policy</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/oag/insurancefraud/pdfs/aicra-act.pdf</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim text of the enacted statute (session law), hosted on nj.gov.</t>
+        </is>
+      </c>
+      <c r="E114" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="B115" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="D115" s="28" t="inlineStr">
+        <is>
+          <t>Official NJDOBI consumer guide PDF, read directly.</t>
+        </is>
+      </c>
+      <c r="E115" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -26281,6 +26444,1122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Standard Policy bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$35,000 (raised from $25,000, effective for policies issued/renewed on or after January 1, 2026)</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3, as amended by P.L.2022, c.87; NJDOBI Bulletin 25-06</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Standard Policy bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$70,000 (raised from $50,000, effective for policies issued/renewed on or after January 1, 2026)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3, as amended by P.L.2022, c.87; NJDOBI Bulletin 25-06</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Standard Policy property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000 (unchanged)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3, as amended by P.L.2022, c.87; NJDOBI Bulletin 25-06</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Basic Policy is a separate, lower-cost option not affected by the 2026 increase</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey offers two coverage options: a Standard Policy (minimums above) and a Basic Policy. The 2026 minimum-limit increase (P.L.2022, c.87) does not apply to the Basic Policy, which is governed separately by N.J.S.A. 39:6A-3.1</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI Bulletin 25-06, footnote 1; N.J.S.A. 39:6A-3.1</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L5" s="28" t="inlineStr">
+        <is>
+          <t>This resolves a previously logged conflict between sources describing different limits: both were correct, describing two different coexisting policy types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Basic Policy personal injury protection (medical expense benefits)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>$15,000 per person per accident; except that benefits are paid up to $250,000 for medically necessary treatment of permanent or significant brain injury, spinal cord injury, or disfigurement</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3.1(a), enacted by P.L.1998, c.21, section 4</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>P.L.1998, c.21 (AICRA) - N.J.S.A. 39:6A-3.1, Basic Automobile Insurance Policy</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/oag/insurancefraud/pdfs/aicra-act.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Basic Policy property damage liability</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3.1(b), enacted by P.L.1998, c.21, section 4</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>P.L.1998, c.21 (AICRA) - N.J.S.A. 39:6A-3.1, Basic Automobile Insurance Policy</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/oag/insurancefraud/pdfs/aicra-act.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Basic Policy optional bodily injury liability</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>An optional $10,000 bodily injury/death liability coverage may be added to a Basic Policy; it does not include this coverage by default</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>N.J.S.A. 39:6A-3.1(c), enacted by P.L.1998, c.21, section 4</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>P.L.1998, c.21 (AICRA) - N.J.S.A. 39:6A-3.1, Basic Automobile Insurance Policy</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/oag/insurancefraud/pdfs/aicra-act.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Coverage structure</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Basic coverage parts (A-F)</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Coverage A (Dwelling): insured damage to the home; Coverage B (Other Structures): usually limited to 10% of Coverage A; Coverage C (Personal Property): typically 50% of Coverage A, paid at Actual Cash Value unless a replacement-cost endorsement is purchased; Coverage D (Loss of Use): usually limited to 20% of Coverage A; Coverage E (Personal Liability): a limited dollar value such as $100,000 or $500,000; Coverage F (Medical Payments to Others): generally limited to $1,000 per person</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, pp. 1-2</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Exclusions</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Flood damage excluded</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Homeowners policies exclude water damage caused by flood; NFIP flood coverage is available to residents of communities that participate in the National Flood Insurance Program (not limited to designated flood zones)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 3</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Exclusions</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Other common exclusions</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Policies also exclude damage from war, nuclear hazard, neglect, earth movement (earthquake), and power failure originating off premises; additional cost of repairs due to building-code changes; home-based business liability; and oil tank pollution cleanup (1st or 3rd party) unless separately purchased</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 4</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Exclusions</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Sewer backup / sump pump overflow</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Not covered by a standard policy; limited coverage (usually up to $5,000) is available only as a separate endorsement</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, pp. 3-4</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey Insurance Underwriting Association (NJIUA)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Market of last resort for homes, mobile homes, rental units, and most commercial property when coverage is unavailable in the admitted or surplus lines markets; the basic policy covers fire, lightning, wind, and smoke only (no theft or liability coverage), though optional theft coverage is available as an endorsement</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 6</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>Contact: NJIUA, 744 Broad Street, PO Box 32609, Newark, NJ 07102; 973-622-3838; www.njiua.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Deductibles</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Hurricane deductible</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Common hurricane deductibles are a percentage (1%, 2%, 5%, or 10%) of Coverage A, triggered only when the National Weather Service designates a hurricane with sustained winds of at least 74 mph measured anywhere in New Jersey; separate from the standard all-peril deductible</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 8</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Deductibles</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Windstorm/hail deductible</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>An optional separate deductible for wind/hail perils can be selected as a fixed dollar amount or as a percentage of Coverage A, up to 10%</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 8</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>New policy cancellation window</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>An insurer may cancel a new policy for any lawful reason within the first 60 days; the cancellation requires at least 10 days' written notice</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, pp. 12-13</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Non-renewal notice</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>An insurer must give written notice of non-renewal, stating the reason, at least 30 days before the policy's expiration date</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 13</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Common discounts</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Insurers commonly offer discounts for multi-policy (home and auto) bundling, protective devices (smoke detectors, alarm/sprinkler systems), nonsmoker households, and long-time policyholders</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, p. 9</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Replacement cost vs Actual Cash Value</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Homeowner policies typically provide replacement cost coverage for the dwelling (Coverage A) but settle personal property at Actual Cash Value (replacement cost minus depreciation) unless a replacement-cost endorsement is purchased</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI consumer guide, pp. 1, 7-8</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>NJDOBI - Insuring Your Home: A Consumer Guide to Homeowners, Renters and Condominium Insurance</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/dobi/division_consumers/pdf/insuringyourhome.pdf</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -32983,26 +34262,26 @@
       <c r="F32" s="41" t="n"/>
       <c r="G32" s="41" t="inlineStr">
         <is>
-          <t>UM/UIM limits also rising</t>
+          <t>UM/UIM limits also rising under P.L.2022, c.87</t>
         </is>
       </c>
       <c r="H32" s="41" t="inlineStr">
         <is>
-          <t>New limits effective Jan 1, 2026 (3 sources)</t>
+          <t>New Standard Policy limits effective Jan 1, 2026, confirmed by NJDOBI Bulletin 25-06</t>
         </is>
       </c>
       <c r="I32" s="41" t="inlineStr">
         <is>
-          <t>CarInsurance.com - Minimum liability by state (Apr 2026)</t>
+          <t>NJ DOBI Bulletin No. 25-06 - Increased Minimum Automobile Insurance Liability Limits</t>
         </is>
       </c>
       <c r="J32" s="42" t="inlineStr">
         <is>
-          <t>https://www.carinsurance.com/Articles/minimum-liability-car-insurance-requirements-by-state.aspx</t>
+          <t>https://www.nj.gov/dobi/bulletins/blt25_06.pdf</t>
         </is>
       </c>
       <c r="K32" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L32" s="41" t="inlineStr">
         <is>
@@ -33011,20 +34290,20 @@
       </c>
       <c r="M32" s="41" t="inlineStr">
         <is>
-          <t>Reference data (secondary source)</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N32" s="46" t="inlineStr">
         <is>
-          <t>Conflicting</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O32" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P32" s="41" t="inlineStr">
         <is>
-          <t>Coverage Criteria (Feb 2026) still lists older two-tier structure (Basic Policy: no BI minimum, $5K PD, $15K PIP; Standard: 15/30/5 + $15K PIP). Confirm with NJ DOBI.</t>
+          <t>Standard Policy minimums. A separate Basic Policy option exists under N.J.S.A. 39:6A-3.1 with PIP $15,000/person, PD $5,000, and optional BI $10,000 - unaffected by this 2026 increase.</t>
         </is>
       </c>
     </row>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -36,6 +36,8 @@
     <sheet name="GA Home Verified" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="NC Auto Verified" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="NC Home Verified" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="VA Auto Verified" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="VA Home Verified" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -705,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -727,7 +729,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia and North Carolina home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina and Virginia auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina and Virginia home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1475,19 +1477,19 @@
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C39">
+      <c r="C39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D39">
+      <c r="D39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E39">
+      <c r="E39" s="28">
         <f>COUNTIF('NC Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F39">
+      <c r="F39" s="28">
         <f>SUM(B39:E39)</f>
         <v/>
       </c>
@@ -1495,282 +1497,316 @@
     <row r="40" ht="15" customHeight="1" s="29">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B40" s="39">
-        <f>SUM(B17:B39)</f>
+        <f>COUNTIF('VA Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C40">
-        <f>SUM(C17:C39)</f>
+      <c r="C40" s="28">
+        <f>COUNTIF('VA Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D40">
-        <f>SUM(D17:D39)</f>
+      <c r="D40" s="28">
+        <f>COUNTIF('VA Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E40">
-        <f>SUM(E17:E39)</f>
+      <c r="E40" s="28">
+        <f>COUNTIF('VA Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F40">
-        <f>SUM(F17:F39)</f>
+      <c r="F40" s="28">
+        <f>SUM(B40:E40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="29">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>VA Home Verified</t>
+        </is>
+      </c>
+      <c r="B41" s="39">
+        <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D41">
+        <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>SUM(B41:E41)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="29">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B42" s="39">
+        <f>SUM(B17:B41)</f>
+        <v/>
+      </c>
+      <c r="C42">
+        <f>SUM(C17:C41)</f>
+        <v/>
+      </c>
+      <c r="D42">
+        <f>SUM(D17:D41)</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>SUM(E17:E41)</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>SUM(F17:F41)</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="29">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="n"/>
+          <t>Conflicts Log</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Where sources disagree and what to verify.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
@@ -1782,84 +1818,132 @@
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
+          <t>IL Home Verified</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>PA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
           <t>PA Home Verified</t>
         </is>
       </c>
-      <c r="B65" s="28" t="inlineStr">
+      <c r="B67" s="28" t="inlineStr">
         <is>
           <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>GA Auto Verified</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" s="28" t="inlineStr">
         <is>
           <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>GA Home Verified</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" s="28" t="inlineStr">
         <is>
           <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>NC Auto Verified</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>NC Home Verified</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VA Home Verified</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
@@ -1871,13 +1955,14 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B10:F10"/>
@@ -1888,7 +1973,6 @@
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10894,10 +10978,14 @@
       </c>
       <c r="F2" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G2" s="41" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" s="41" t="inlineStr">
+        <is>
+          <t>Not actually conflicting. VA DMV confirms current minimums are 50/100/25, effective Jan 1, 2025. The 30/60/20 figure (Coverage Criteria) was the prior minimum, in effect Jan 1, 2022 - Dec 31, 2024.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="29">
       <c r="A3" s="41" t="inlineStr">
@@ -13440,7 +13528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16189,6 +16277,56 @@
         </is>
       </c>
       <c r="E112" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="B113" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>Official Virginia DMV consumer page, read directly.</t>
+        </is>
+      </c>
+      <c r="E113" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Virginia's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E114" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -26281,6 +26419,794 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$50,000 (raised from $30,000, effective for policies on or after January 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$100,000 (raised from $60,000, effective for policies on or after January 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000 (raised from $20,000, effective for policies on or after January 1, 2025)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Continuous coverage required while registered</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Code Section 46.2-706 requires every registered motor vehicle to be insured by a liability policy from a Virginia-licensed insurer, and the vehicle must remain insured while registered whether or not it is actually operated</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Va. Code Ann. Section 46.2-706; VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motor vehicle fee eliminated</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia ended its long-standing 'uninsured motor vehicle fee' option (which allowed paying a fee instead of carrying insurance) effective July 1, 2024; every registered vehicle must now carry actual liability insurance</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Penalties for an uninsured vehicle</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>DMV suspends the owner's driver's license, vehicle registration, and license plates for an uninsured vehicle until the owner pays a $600 non-compliance fee, furnishes and maintains SR-22 proof of financial responsibility for three years, and pays a reinstatement fee if applicable; a Payment Plan Program is available for eligible owners to spread out the statutory fee</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>VA DMV insurance requirements page</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Virginia DMV - Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Virginia Property Insurance Association (VPIA) is Virginia's FAIR Plan, a market of last resort providing dwelling, commercial, condominium, tenant-contents, and landlord (absentee-owner) property coverage for applicants unable to obtain it in the standard market</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Optional endorsements</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Optional endorsements including theft, replacement cost, liability, and ordinance-and-law coverage are available subject to underwriting approval</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Base policy exclusions</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>The base FP-1 policy form excludes water damage and does not include Additional Living Expenses coverage (ALE is available only on the broader FP-2 form); no liability coverage is provided for non-owner-occupied dwellings</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Annual reapplication</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>VPIA policies are not automatically renewed; policyholders must reapply annually</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Underwriting restriction on animals</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage may be canceled if prohibited animals are kept on the property, including certain dog breeds and farm animals such as chickens, rabbits, horses, goats, pigs, and snakes</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Virginia FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Phone (804) 591-3700 or (800) 899-7973, Monday-Friday 8:00 AM-4:30 PM; underwriting@vpia.com; claims@vpia.com</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>VPIA FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Virginia Property Insurance Association (VPIA) - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.vpia.com/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -33816,21 +34742,21 @@
       <c r="G48" s="41" t="n"/>
       <c r="H48" s="41" t="inlineStr">
         <is>
-          <t>Effective Jan 1, 2025 per two sources</t>
+          <t>New limits effective Jan 1, 2025, confirmed directly by VA DMV</t>
         </is>
       </c>
       <c r="I48" s="41" t="inlineStr">
         <is>
-          <t>CarInsurance.com - Minimum liability by state (Apr 2026)</t>
+          <t>Virginia DMV - Insurance Requirements</t>
         </is>
       </c>
       <c r="J48" s="42" t="inlineStr">
         <is>
-          <t>https://www.carinsurance.com/Articles/minimum-liability-car-insurance-requirements-by-state.aspx</t>
+          <t>https://www.dmv.virginia.gov/vehicles/insurance-requirements</t>
         </is>
       </c>
       <c r="K48" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L48" s="41" t="inlineStr">
         <is>
@@ -33839,20 +34765,20 @@
       </c>
       <c r="M48" s="41" t="inlineStr">
         <is>
-          <t>Reference data (secondary source)</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N48" s="46" t="inlineStr">
         <is>
-          <t>Conflicting</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O48" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P48" s="41" t="inlineStr">
         <is>
-          <t>Coverage Criteria says 30/60/20 effective Jan 1, 2025. Two sources agree on 50/100/25. Confirm with VA DMV.</t>
+          <t>The $30,000/$60,000/$20,000 figure some sources list was the prior minimum, in effect Jan 1, 2022 - Dec 31, 2024.</t>
         </is>
       </c>
     </row>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -40,6 +40,8 @@
     <sheet name="NJ Home Verified" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="VA Auto Verified" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="VA Home Verified" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="WA Auto Verified" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="WA Home Verified" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -709,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -732,7 +734,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey and Virginia auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey and Virginia home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia and Washington auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia and Washington home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1590,19 +1592,19 @@
         <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C43">
+      <c r="C43" s="28">
         <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D43">
+      <c r="D43" s="28">
         <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E43">
+      <c r="E43" s="28">
         <f>COUNTIF('VA Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F43">
+      <c r="F43" s="28">
         <f>SUM(B43:E43)</f>
         <v/>
       </c>
@@ -1610,286 +1612,316 @@
     <row r="44" ht="15" customHeight="1" s="29">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B44" s="39">
-        <f>SUM(B17:B43)</f>
+        <f>COUNTIF('WA Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C44">
-        <f>SUM(C17:C43)</f>
+      <c r="C44" s="28">
+        <f>COUNTIF('WA Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D44">
-        <f>SUM(D17:D43)</f>
+      <c r="D44" s="28">
+        <f>COUNTIF('WA Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E44">
-        <f>SUM(E17:E43)</f>
+      <c r="E44" s="28">
+        <f>COUNTIF('WA Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F44">
-        <f>SUM(F17:F43)</f>
+      <c r="F44" s="28">
+        <f>SUM(B44:E44)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="29">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>WA Home Verified</t>
+        </is>
+      </c>
+      <c r="B45" s="39">
+        <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C45">
+        <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E45">
+        <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F45">
+        <f>SUM(B45:E45)</f>
+        <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>SUM(B17:B45)</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>SUM(C17:C45)</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>SUM(D17:D45)</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>SUM(E17:E45)</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>SUM(F17:F45)</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
@@ -1901,132 +1933,180 @@
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
+          <t>GA Home Verified</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="inlineStr">
+        <is>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>NC Auto Verified</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
           <t>NC Home Verified</t>
         </is>
       </c>
-      <c r="B73" s="28" t="inlineStr">
+      <c r="B75" s="28" t="inlineStr">
         <is>
           <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>NJ Auto Verified</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" s="28" t="inlineStr">
         <is>
           <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>NJ Home Verified</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" s="28" t="inlineStr">
         <is>
           <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>VA Auto Verified</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>VA Home Verified</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>WA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WA Home Verified</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
@@ -2035,9 +2115,9 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B52:F52"/>
@@ -2045,6 +2125,7 @@
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B53:F53"/>
@@ -2054,7 +2135,6 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B50:F50"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -13615,7 +13695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16489,6 +16569,56 @@
         </is>
       </c>
       <c r="E117" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="B118" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="D118" s="28" t="inlineStr">
+        <is>
+          <t>Official Washington OIC consumer page, read directly.</t>
+        </is>
+      </c>
+      <c r="E118" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="B119" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="D119" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Washington's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E119" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -28485,6 +28615,741 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>WA OIC mandatory insurance law page (25/50/10)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>WA OIC mandatory insurance law page (25/50/10)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>WA OIC mandatory insurance law page (25/50/10)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Alternatives to carrying insurance</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Instead of liability insurance, a driver may file a certificate of deposit with the Department of Licensing, or a liability bond of at least $60,000 from an authorized surety bond company; self-insurance is available only to those with 26 or more vehicles</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>WA OIC mandatory insurance law page</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Proof-of-insurance requirement</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>If stopped by a law enforcement officer, a driver must show proof of auto/motorcycle insurance; failure to do so results in a traffic violation ticket</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>WA OIC mandatory insurance law page</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Washington FAIR ('Fair Access to Insurance Requirements') Plan was established in 1968 to provide basic property insurance to applicants who cannot obtain property insurance in the standard insurance market; it is a Joint Reinsurance Association, with every insurer licensed to write property insurance in the state required to be a member, and receives no taxpayer or state funding</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage provided</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Basic fire insurance for owner- and tenant-occupied dwellings, apartment buildings, commercial structures, and personal property/contents; Extended Coverage and Vandalism coverage are available</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Exclusions</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage for liability, theft, and most types of water-related losses is not available through the Plan</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>A last-resort option limited to applicants who are unable to obtain property coverage in the standard insurance market</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Deductibles</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>A range of deductibles is available, similar to standard-market policies</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>2122 164th Street SW, Suite 301, Lynnwood, WA 98087; (425) 745-9808 or (866) 745-9808; wafairplan@wafairplan.com</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>WA FAIR Plan FAQ (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Washington FAIR Plan - Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wafairplan.com/faq/</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -36066,17 +36931,31 @@
           <t>Washington</t>
         </is>
       </c>
-      <c r="B49" s="41" t="n"/>
-      <c r="C49" s="41" t="n"/>
-      <c r="D49" s="41" t="n"/>
+      <c r="B49" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C49" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D49" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E49" s="41" t="n"/>
       <c r="F49" s="41" t="n"/>
       <c r="G49" s="41" t="n"/>
       <c r="H49" s="41" t="n"/>
-      <c r="I49" s="41" t="n"/>
-      <c r="J49" s="42" t="n"/>
+      <c r="I49" s="41" t="inlineStr">
+        <is>
+          <t>Washington OIC - Mandatory Auto/Motorcycle Insurance Law</t>
+        </is>
+      </c>
+      <c r="J49" s="42" t="inlineStr">
+        <is>
+          <t>https://www.insurance.wa.gov/washington-states-mandatory-automotorcycle-insurance-law</t>
+        </is>
+      </c>
       <c r="K49" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L49" s="41" t="inlineStr">
         <is>
@@ -36085,16 +36964,16 @@
       </c>
       <c r="M49" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N49" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O49" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P49" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -42,6 +42,8 @@
     <sheet name="VA Home Verified" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="WA Auto Verified" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="WA Home Verified" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="AZ Auto Verified" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="AZ Home Verified" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -711,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -734,7 +736,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia and Washington auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia and Washington home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington and Arizona auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington and Arizona home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1646,19 +1648,19 @@
         <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C45">
+      <c r="C45" s="28">
         <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D45">
+      <c r="D45" s="28">
         <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E45">
+      <c r="E45" s="28">
         <f>COUNTIF('WA Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F45">
+      <c r="F45" s="28">
         <f>SUM(B45:E45)</f>
         <v/>
       </c>
@@ -1666,286 +1668,316 @@
     <row r="46" ht="15" customHeight="1" s="29">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>AZ Auto Verified</t>
         </is>
       </c>
       <c r="B46" s="39">
-        <f>SUM(B17:B45)</f>
+        <f>COUNTIF('AZ Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C46">
-        <f>SUM(C17:C45)</f>
+      <c r="C46" s="28">
+        <f>COUNTIF('AZ Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D46">
-        <f>SUM(D17:D45)</f>
+      <c r="D46" s="28">
+        <f>COUNTIF('AZ Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E46">
-        <f>SUM(E17:E45)</f>
+      <c r="E46" s="28">
+        <f>COUNTIF('AZ Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F46">
-        <f>SUM(F17:F45)</f>
+      <c r="F46" s="28">
+        <f>SUM(B46:E46)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="29">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B47" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>AZ Home Verified</t>
+        </is>
+      </c>
+      <c r="B47" s="39">
+        <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>SUM(B47:E47)</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B48" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B48" s="39">
+        <f>SUM(B17:B47)</f>
+        <v/>
+      </c>
+      <c r="C48">
+        <f>SUM(C17:C47)</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>SUM(D17:D47)</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>SUM(E17:E47)</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>SUM(F17:F47)</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
@@ -1957,172 +1989,218 @@
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
+          <t>NC Home Verified</t>
+        </is>
+      </c>
+      <c r="B77" s="28" t="inlineStr">
+        <is>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>NJ Auto Verified</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
           <t>NJ Home Verified</t>
         </is>
       </c>
-      <c r="B77" s="28" t="inlineStr">
+      <c r="B79" s="28" t="inlineStr">
         <is>
           <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>VA Auto Verified</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" s="28" t="inlineStr">
         <is>
           <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t>VA Home Verified</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" s="28" t="inlineStr">
         <is>
           <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>WA Auto Verified</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>WA Home Verified</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AZ Auto Verified</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AZ Home Verified</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B61:F61"/>
@@ -2133,8 +2211,10 @@
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B64:F64"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B50:F50"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -13695,7 +13775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16619,6 +16699,106 @@
         </is>
       </c>
       <c r="E119" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="B120" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
+      <c r="D120" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from azleg.gov.</t>
+        </is>
+      </c>
+      <c r="E120" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4135 - Evidence of Financial Responsibility; Violation; Penalties</t>
+        </is>
+      </c>
+      <c r="B121" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04135.htm</t>
+        </is>
+      </c>
+      <c r="D121" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from azleg.gov.</t>
+        </is>
+      </c>
+      <c r="E121" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-2202 - Joint Underwriting Association (liability only)</t>
+        </is>
+      </c>
+      <c r="B122" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/02202.htm</t>
+        </is>
+      </c>
+      <c r="D122" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from azleg.gov.</t>
+        </is>
+      </c>
+      <c r="E122" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-1652 - Cancellation and Nonrenewal of Property Insurance</t>
+        </is>
+      </c>
+      <c r="B123" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/01652.htm</t>
+        </is>
+      </c>
+      <c r="D123" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from azleg.gov.</t>
+        </is>
+      </c>
+      <c r="E123" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -29350,6 +29530,635 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000 (raised from $15,000, for policies issued/renewed on or after July 1, 2020)</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 28-4009</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000 (raised from $30,000, for policies issued/renewed on or after July 1, 2020)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 28-4009</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$15,000 (raised from $10,000, for policies issued/renewed on or after July 1, 2020)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 28-4009</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Self-insurance exception</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Policies issued to a person holding a valid self-insurance certificate under A.R.S. Section 28-4007 continue to follow the pre-July-2020 limits ($15,000/$30,000/$10,000)</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 28-4009</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Penalties for lapses in coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Tiered civil penalties and license/registration suspensions within a rolling 36-month period: 1st violation, minimum $500 penalty and a 3-month driving-privilege restriction; 2nd violation, minimum $750 penalty and a 6-month suspension of license, registration, and plates; 3rd or later violation, minimum $1,000 penalty and a 1-year suspension, with reinstatement requiring filed proof of financial responsibility</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 28-4135</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4135 - Evidence of Financial Responsibility; Violation; Penalties</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04135.htm</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>No state FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona has no property/dwelling market-of-last-resort plan</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona's only joint underwriting association statute (A.R.S. Section 20-2202) is limited to liability insurance, explicitly operating only when 'liability insurance is substantially unavailable through private insurers'; it does not cover property or dwelling insurance, so Arizona - unlike many other states - has no state-run FAIR Plan equivalent for homeowners</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 20-2202</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-2202 - Joint Underwriting Association (liability only)</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/02202.htm</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>60-day mid-term cancellation protection</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>After a property insurance policy has been in effect 60 days (or immediately, for a renewal), a cancellation notice is effective only if based on specific grounds: nonpayment of premium, the insured's conviction of a hazard-increasing crime, fraud or material misrepresentation, grossly negligent acts substantially increasing the hazard, an unforeseen substantial change in risk, a state-law violation found by the Director, or the insured's failure to take reasonable steps to fix a condition that contributed to a loss</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 20-1652(A)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-1652 - Cancellation and Nonrenewal of Property Insurance</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/01652.htm</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Premises-condition remedy process</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>If non-renewal is based on the condition of the premises, the insured must first be given 30 days' notice to remedy the identified conditions; if remedied, coverage must be renewed; if not satisfactorily remedied, the insured gets an additional 30 days (on payment of premium) to cure the defect</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 20-1652(B)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-1652 - Cancellation and Nonrenewal of Property Insurance</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/01652.htm</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage-inquiry protection</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>An insurer may not use an insured's inquiry about their policy's coverage or terms as a basis for declining, nonrenewing, or canceling that coverage or a binder of coverage</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>A.R.S. Section 20-1652(F)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 20-1652 - Cancellation and Nonrenewal of Property Insurance</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/20/01652.htm</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -34645,17 +35454,35 @@
           <t>Arizona</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n"/>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
+      <c r="B4" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="E4" s="41" t="n"/>
       <c r="F4" s="41" t="n"/>
       <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
-      <c r="I4" s="41" t="n"/>
-      <c r="J4" s="42" t="n"/>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>Raised from 15/30/10, effective for policies issued/renewed on or after July 1, 2020</t>
+        </is>
+      </c>
+      <c r="I4" s="41" t="inlineStr">
+        <is>
+          <t>Arizona Revised Statutes 28-4009 - Motor Vehicle Liability Policy Requirements</t>
+        </is>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
+        <is>
+          <t>https://www.azleg.gov/ars/28/04009.htm</t>
+        </is>
+      </c>
       <c r="K4" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L4" s="41" t="inlineStr">
         <is>
@@ -34664,16 +35491,16 @@
       </c>
       <c r="M4" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O4" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P4" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -44,6 +44,8 @@
     <sheet name="WA Home Verified" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="AZ Auto Verified" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="AZ Home Verified" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="TN Auto Verified" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="TN Home Verified" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -713,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -736,7 +738,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington and Arizona auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington and Arizona home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona and Tennessee auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona and Tennessee home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1702,19 +1704,19 @@
         <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C47">
+      <c r="C47" s="28">
         <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D47">
+      <c r="D47" s="28">
         <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E47">
+      <c r="E47" s="28">
         <f>COUNTIF('AZ Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F47">
+      <c r="F47" s="28">
         <f>SUM(B47:E47)</f>
         <v/>
       </c>
@@ -1722,286 +1724,316 @@
     <row r="48" ht="15" customHeight="1" s="29">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>TN Auto Verified</t>
         </is>
       </c>
       <c r="B48" s="39">
-        <f>SUM(B17:B47)</f>
+        <f>COUNTIF('TN Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C48">
-        <f>SUM(C17:C47)</f>
+      <c r="C48" s="28">
+        <f>COUNTIF('TN Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D48">
-        <f>SUM(D17:D47)</f>
+      <c r="D48" s="28">
+        <f>COUNTIF('TN Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E48">
-        <f>SUM(E17:E47)</f>
+      <c r="E48" s="28">
+        <f>COUNTIF('TN Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F48">
-        <f>SUM(F17:F47)</f>
+      <c r="F48" s="28">
+        <f>SUM(B48:E48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="29">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B49" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>TN Home Verified</t>
+        </is>
+      </c>
+      <c r="B49" s="39">
+        <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C49">
+        <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>SUM(B49:E49)</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B50" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B50" s="39">
+        <f>SUM(B17:B49)</f>
+        <v/>
+      </c>
+      <c r="C50">
+        <f>SUM(C17:C49)</f>
+        <v/>
+      </c>
+      <c r="D50">
+        <f>SUM(D17:D49)</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>SUM(E17:E49)</f>
+        <v/>
+      </c>
+      <c r="F50">
+        <f>SUM(F17:F49)</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
@@ -2013,180 +2045,228 @@
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
+          <t>NJ Home Verified</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>VA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B82" s="28" t="inlineStr">
+        <is>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr">
+        <is>
           <t>VA Home Verified</t>
         </is>
       </c>
-      <c r="B81" s="28" t="inlineStr">
+      <c r="B83" s="28" t="inlineStr">
         <is>
           <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>WA Auto Verified</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" s="28" t="inlineStr">
         <is>
           <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>WA Home Verified</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" s="28" t="inlineStr">
         <is>
           <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>AZ Auto Verified</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>AZ Home Verified</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TN Auto Verified</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TN Home Verified</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
         </is>
       </c>
     </row>
@@ -2197,6 +2277,7 @@
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B66:F66"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B52:F52"/>
@@ -2208,14 +2289,13 @@
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B50:F50"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13775,7 +13855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -16799,6 +16879,156 @@
         </is>
       </c>
       <c r="E123" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 55-12-102 - Financial Responsibility Definitions</t>
+        </is>
+      </c>
+      <c r="B124" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C124" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-55-motor-and-other-vehicles/tn-code-sect-55-12-102/</t>
+        </is>
+      </c>
+      <c r="D124" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Tennessee Code Annotated); no free official .gov host exists for the current codified text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E124" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-1303 - Notice of Cancellation</t>
+        </is>
+      </c>
+      <c r="B125" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-1303/</t>
+        </is>
+      </c>
+      <c r="D125" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Tennessee Code Annotated), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E125" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-1304 - Notice of Intention Not to Renew</t>
+        </is>
+      </c>
+      <c r="B126" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C126" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-1304/</t>
+        </is>
+      </c>
+      <c r="D126" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Tennessee Code Annotated), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E126" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="28" t="inlineStr">
+        <is>
+          <t>NAIC - Fair Access to Insurance Requirements (FAIR) Plans</t>
+        </is>
+      </c>
+      <c r="B127" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>https://content.naic.org/insurance-topics/fair-access-to-insurance-requirements-plans</t>
+        </is>
+      </c>
+      <c r="D127" s="28" t="inlineStr">
+        <is>
+          <t>NAIC is the national association of state insurance regulators; its own published list of FAIR Plan states.</t>
+        </is>
+      </c>
+      <c r="E127" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-113 - Homeowner's Insurance Inquiry Protection</t>
+        </is>
+      </c>
+      <c r="B128" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C128" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-113/</t>
+        </is>
+      </c>
+      <c r="D128" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Tennessee Code Annotated), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E128" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-114 - Certificate of Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="B129" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-114/</t>
+        </is>
+      </c>
+      <c r="D129" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Tennessee Code Annotated), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E129" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -30159,6 +30389,587 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 55-12-102(12)(D)(i)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 55-12-102 - Financial Responsibility Definitions</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-55-motor-and-other-vehicles/tn-code-sect-55-12-102/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 55-12-102(12)(D)(i)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 55-12-102 - Financial Responsibility Definitions</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-55-motor-and-other-vehicles/tn-code-sect-55-12-102/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000 (or a single-limit policy of at least $65,000)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 55-12-102(12)(D)(i)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 55-12-102 - Financial Responsibility Definitions</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-55-motor-and-other-vehicles/tn-code-sect-55-12-102/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>Effective for proof of financial responsibility required after December 31, 2022; a policy already compliant on that date is not in violation if it meets these limits by its first renewal after that date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation notice period</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>20 days' notice generally; 10 days' notice if due to nonpayment or if the policy has been in effect less than 60 days and is not a renewal; insured may request the reasons for cancellation in writing within 15 days of the effective date</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 56-7-1303</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-1303 - Notice of Cancellation</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-1303/</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Nonrenewal notice period</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>30 days' notice of intent not to renew; insured may request written reasons within 15 days of the nonrenewal's effective date, and the insurer must respond within 20 days</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 56-7-1304</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-1304 - Notice of Intention Not to Renew</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-1304/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>No state FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee has no state-run FAIR Plan</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The NAIC's own list of states with a FAIR (Fair Access to Insurance Requirements) Plan - 33 states as of its most recent count - does not include Tennessee, meaning homeowners who cannot find coverage in the standard or surplus lines markets have no state-backed insurer of last resort to fall back on</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>NAIC FAIR Plans overview</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>NAIC - Fair Access to Insurance Requirements (FAIR) Plans</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://content.naic.org/insurance-topics/fair-access-to-insurance-requirements-plans</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Homeowner inquiry protection</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>An insurer may not increase a premium or cancel a homeowner's insurance policy solely because the insured made an inquiry about their policy or a loss under it; the insurer may only treat a communication as a claim if its own investigation produces a written finding of a changed condition at the property or a fraudulent act by the consumer</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 56-7-113</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-113 - Homeowner's Insurance Inquiry Protection</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-113/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Certificates of insurance cannot alter actual coverage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>A certificate of insurance - a document showing evidence of property or casualty coverage - can never amend, extend, or alter the coverage actually provided by the underlying policy; preparing a misleading certificate is a violation subject to civil penalties of up to $1,000 per violation</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Tenn. Code Ann. Section 56-7-114</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee Code Annotated 56-7-114 - Certificate of Insurance Requirements</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/tn/title-56-insurance/tn-code-sect-56-7-114/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -37482,19 +38293,23 @@
       <c r="E44" s="41" t="n"/>
       <c r="F44" s="41" t="n"/>
       <c r="G44" s="41" t="n"/>
-      <c r="H44" s="41" t="n"/>
+      <c r="H44" s="41" t="inlineStr">
+        <is>
+          <t>Current limits apply to proof of financial responsibility required after December 31, 2022</t>
+        </is>
+      </c>
       <c r="I44" s="41" t="inlineStr">
         <is>
-          <t>AutoInsurance.org - Requirements by state</t>
+          <t>Tennessee Code Annotated 55-12-102 - Financial Responsibility Definitions</t>
         </is>
       </c>
       <c r="J44" s="42" t="inlineStr">
         <is>
-          <t>https://www.autoinsurance.org/car-insurance-requirements/</t>
+          <t>https://codes.findlaw.com/tn/title-55-motor-and-other-vehicles/tn-code-sect-55-12-102/</t>
         </is>
       </c>
       <c r="K44" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L44" s="41" t="inlineStr">
         <is>
@@ -37503,18 +38318,22 @@
       </c>
       <c r="M44" s="41" t="inlineStr">
         <is>
-          <t>Reference data (secondary source)</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N44" s="45" t="inlineStr">
         <is>
-          <t>Secondary - unverified</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O44" s="43" t="n">
-        <v>46295</v>
-      </c>
-      <c r="P44" s="41" t="n"/>
+        <v>46296</v>
+      </c>
+      <c r="P44" s="41" t="inlineStr">
+        <is>
+          <t>Single-limit alternative: at least $65,000 per accident.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="35.05" customHeight="1" s="29">
       <c r="A45" s="41" t="inlineStr">

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -46,6 +46,8 @@
     <sheet name="AZ Home Verified" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="TN Auto Verified" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="TN Home Verified" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="IN Auto Verified" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="IN Home Verified" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -715,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -738,7 +740,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona and Tennessee auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona and Tennessee home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee and Indiana auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee and Indiana home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1758,19 +1760,19 @@
         <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C49">
+      <c r="C49" s="28">
         <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D49">
+      <c r="D49" s="28">
         <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E49">
+      <c r="E49" s="28">
         <f>COUNTIF('TN Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F49">
+      <c r="F49" s="28">
         <f>SUM(B49:E49)</f>
         <v/>
       </c>
@@ -1778,286 +1780,316 @@
     <row r="50" ht="15" customHeight="1" s="29">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>IN Auto Verified</t>
         </is>
       </c>
       <c r="B50" s="39">
-        <f>SUM(B17:B49)</f>
+        <f>COUNTIF('IN Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C50">
-        <f>SUM(C17:C49)</f>
+      <c r="C50" s="28">
+        <f>COUNTIF('IN Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D50">
-        <f>SUM(D17:D49)</f>
+      <c r="D50" s="28">
+        <f>COUNTIF('IN Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E50">
-        <f>SUM(E17:E49)</f>
+      <c r="E50" s="28">
+        <f>COUNTIF('IN Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F50">
-        <f>SUM(F17:F49)</f>
+      <c r="F50" s="28">
+        <f>SUM(B50:E50)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="29">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B51" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>IN Home Verified</t>
+        </is>
+      </c>
+      <c r="B51" s="39">
+        <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C51">
+        <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D51">
+        <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E51">
+        <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F51">
+        <f>SUM(B51:E51)</f>
+        <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B52" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B52" s="39">
+        <f>SUM(B17:B51)</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>SUM(C17:C51)</f>
+        <v/>
+      </c>
+      <c r="D52">
+        <f>SUM(D17:D51)</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>SUM(E17:E51)</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>SUM(F17:F51)</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
@@ -2069,204 +2101,252 @@
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
+          <t>VA Home Verified</t>
+        </is>
+      </c>
+      <c r="B85" s="28" t="inlineStr">
+        <is>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>WA Auto Verified</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
           <t>WA Home Verified</t>
         </is>
       </c>
-      <c r="B85" s="28" t="inlineStr">
+      <c r="B87" s="28" t="inlineStr">
         <is>
           <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>AZ Auto Verified</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" s="28" t="inlineStr">
         <is>
           <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
         <is>
           <t>AZ Home Verified</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" s="28" t="inlineStr">
         <is>
           <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>TN Auto Verified</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>TN Home Verified</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IN Auto Verified</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IN Home Verified</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
@@ -2280,21 +2360,21 @@
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -13855,7 +13935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17029,6 +17109,81 @@
         </is>
       </c>
       <c r="E129" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 9-25-4-5 - Financial Responsibility Minimum Limits</t>
+        </is>
+      </c>
+      <c r="B130" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C130" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-9-motor-vehicles/in-code-sect-9-25-4-5.html</t>
+        </is>
+      </c>
+      <c r="D130" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Indiana Code), read via a legal-code aggregator (iga.in.gov is a JS-rendered page that could not be read directly).</t>
+        </is>
+      </c>
+      <c r="E130" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 27-7-5-2 - Uninsured/Underinsured Motorist Coverage</t>
+        </is>
+      </c>
+      <c r="B131" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-27-insurance/in-code-sect-27-7-5-2.html</t>
+        </is>
+      </c>
+      <c r="D131" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Indiana Code), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E131" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="B132" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C132" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="D132" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Indiana's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E132" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -32085,6 +32240,688 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code Section 9-25-4-5</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 9-25-4-5 - Financial Responsibility Minimum Limits</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-9-motor-vehicles/in-code-sect-9-25-4-5.html</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code Section 9-25-4-5</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 9-25-4-5 - Financial Responsibility Minimum Limits</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-9-motor-vehicles/in-code-sect-9-25-4-5.html</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000 (raised from $10,000, effective July 1, 2018)</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code Section 9-25-4-5</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 9-25-4-5 - Financial Responsibility Minimum Limits</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-9-motor-vehicles/in-code-sect-9-25-4-5.html</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured/underinsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Insurers must make UM/UIM coverage available at limits at least equal to the policy's bodily injury liability limits; underinsured motorist coverage may never be sold below $50,000</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code Section 27-7-5-2</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 27-7-5-2 - Uninsured/Underinsured Motorist Coverage</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-27-insurance/in-code-sect-27-7-5-2.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>UM/UIM rejection rules</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>A named insured may reject UM and UIM coverage together, or reject either one separately if the insurer offers the other separately; the rejection must identify which coverage is rejected and its effective date, binds every other person insured under the policy, and the insurer need not re-offer the coverage on renewal or replacement policies unless the insured later requests it in writing</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code Section 27-7-5-2</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana Code 27-7-5-2 - Uninsured/Underinsured Motorist Coverage</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-27-insurance/in-code-sect-27-7-5-2.html</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Indiana Basic Property Insurance Underwriting Association (the Indiana FAIR Plan) was established October 28, 1968 to provide property insurance to applicants unable to obtain coverage in the standard market; it is a last-resort option, not a competing alternative</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Applicants must have been declined coverage by at least three non-related insurance companies, which is verified during the application process</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage provided</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Dwelling insurance and commercial property insurance</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage limits</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Dwellings are capped at a combined $250,000 for building and contents; commercial property is capped at a combined $1,000,000 for building and contents</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>3502 Woodview Trace, Suite 100, Indianapolis, IN 46268; claims 317-692-0572, member questions 317-692-0578, agent/agency access and all other questions 317-692-0559; Monday-Thursday 7:00 AM-4:00 PM, Friday 7:30 AM-11:30 AM (appointment required for visits)</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana FAIR Plan (Indiana Basic Property Insurance Underwriting Association)</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.indianafairplan.com</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -36905,17 +37742,39 @@
           <t>Indiana</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
+      <c r="B16" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="E16" s="41" t="n"/>
       <c r="F16" s="41" t="n"/>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="41" t="n"/>
-      <c r="I16" s="41" t="n"/>
-      <c r="J16" s="42" t="n"/>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>UM/UIM available; UIM cannot be sold below $50,000</t>
+        </is>
+      </c>
+      <c r="H16" s="41" t="inlineStr">
+        <is>
+          <t>Property damage raised from $10,000, effective July 1, 2018</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
+        <is>
+          <t>Indiana Code 9-25-4-5 - Financial Responsibility Minimum Limits</t>
+        </is>
+      </c>
+      <c r="J16" s="42" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/in/title-9-motor-vehicles/in-code-sect-9-25-4-5.html</t>
+        </is>
+      </c>
       <c r="K16" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L16" s="41" t="inlineStr">
         <is>
@@ -36924,16 +37783,16 @@
       </c>
       <c r="M16" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N16" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O16" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P16" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -48,6 +48,8 @@
     <sheet name="TN Home Verified" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="IN Auto Verified" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="IN Home Verified" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="MO Auto Verified" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="MO Home Verified" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -717,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -740,7 +742,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee and Indiana auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee and Indiana home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana and Missouri auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana and Missouri home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1814,19 +1816,19 @@
         <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C51">
+      <c r="C51" s="28">
         <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D51">
+      <c r="D51" s="28">
         <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E51">
+      <c r="E51" s="28">
         <f>COUNTIF('IN Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F51">
+      <c r="F51" s="28">
         <f>SUM(B51:E51)</f>
         <v/>
       </c>
@@ -1834,286 +1836,316 @@
     <row r="52" ht="15" customHeight="1" s="29">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>MO Auto Verified</t>
         </is>
       </c>
       <c r="B52" s="39">
-        <f>SUM(B17:B51)</f>
+        <f>COUNTIF('MO Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C52">
-        <f>SUM(C17:C51)</f>
+      <c r="C52" s="28">
+        <f>COUNTIF('MO Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D52">
-        <f>SUM(D17:D51)</f>
+      <c r="D52" s="28">
+        <f>COUNTIF('MO Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E52">
-        <f>SUM(E17:E51)</f>
+      <c r="E52" s="28">
+        <f>COUNTIF('MO Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F52">
-        <f>SUM(F17:F51)</f>
+      <c r="F52" s="28">
+        <f>SUM(B52:E52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B53" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>MO Home Verified</t>
+        </is>
+      </c>
+      <c r="B53" s="39">
+        <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>SUM(B53:E53)</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B54" s="39">
+        <f>SUM(B17:B53)</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>SUM(C17:C53)</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>SUM(D17:D53)</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>SUM(E17:E53)</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>SUM(F17:F53)</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
@@ -2125,228 +2157,276 @@
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>WA Home Verified</t>
+          <t>VA Home Verified</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>AZ Auto Verified</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
+          <t>WA Home Verified</t>
+        </is>
+      </c>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
+        <is>
+          <t>AZ Auto Verified</t>
+        </is>
+      </c>
+      <c r="B90" s="28" t="inlineStr">
+        <is>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
           <t>AZ Home Verified</t>
         </is>
       </c>
-      <c r="B89" s="28" t="inlineStr">
+      <c r="B91" s="28" t="inlineStr">
         <is>
           <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>TN Auto Verified</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B92" s="28" t="inlineStr">
         <is>
           <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>TN Home Verified</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B93" s="28" t="inlineStr">
         <is>
           <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>IN Auto Verified</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>IN Home Verified</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MO Auto Verified</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MO Home Verified</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2434,12 @@
   <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B54:F54"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B60:F60"/>
@@ -2367,10 +2447,10 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B64:F64"/>
@@ -13935,7 +14015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17184,6 +17264,106 @@
         </is>
       </c>
       <c r="E132" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 303.190 - Motor Vehicle Liability Policy, Contents</t>
+        </is>
+      </c>
+      <c r="B133" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C133" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xix-motor-vehicles-watercraft-and-aviation/mo-rev-st-303-190</t>
+        </is>
+      </c>
+      <c r="D133" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Missouri Revised Statutes), read via a legal-code aggregator (revisor.mo.gov could not be reached directly).</t>
+        </is>
+      </c>
+      <c r="E133" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 379.203 - Uninsured Motorist Coverage Required</t>
+        </is>
+      </c>
+      <c r="B134" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C134" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xxiv-business-and-financial-institutions/mo-rev-st-379-203.html</t>
+        </is>
+      </c>
+      <c r="D134" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text (Missouri Revised Statutes), read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E134" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Property Insurance Placement Facility (Missouri FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="B135" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C135" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com</t>
+        </is>
+      </c>
+      <c r="D135" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Missouri's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E135" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="B136" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C136" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com/general-information.html</t>
+        </is>
+      </c>
+      <c r="D136" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Missouri's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E136" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -32922,6 +33102,635 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes Section 303.190</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 303.190 - Motor Vehicle Liability Policy, Contents</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xix-motor-vehicles-watercraft-and-aviation/mo-rev-st-303-190</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes Section 303.190</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 303.190 - Motor Vehicle Liability Policy, Contents</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xix-motor-vehicles-watercraft-and-aviation/mo-rev-st-303-190</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes Section 303.190</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 303.190 - Motor Vehicle Liability Policy, Contents</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xix-motor-vehicles-watercraft-and-aviation/mo-rev-st-303-190</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Mandatory on every auto liability policy delivered in Missouri, at the same limits as the policy's bodily injury coverage; an 'uninsured motor vehicle' includes one whose insurer cannot pay due to insolvency, but only if that insurer becomes insolvent within two years of the accident, and an insurer paying a UM claim on that basis may not recover more from the at-fault driver than it actually recovers from the insolvent insurer's assets</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes Section 379.203</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 379.203 - Uninsured Motorist Coverage Required</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xxiv-business-and-financial-institutions/mo-rev-st-379-203.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Missouri Property Insurance Placement Facility (Missouri FAIR Plan) was established in October 1969 as a last resort for applicants unable to secure property insurance in the normal insurance market; it is not intended to compete with the voluntary market</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Property Insurance Placement Facility (Missouri FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Shop the standard market first</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Applicants are expected to first try to obtain coverage in the standard market before applying to the FAIR Plan</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com/general-information.html</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage limits</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Per state statute, the maximum policy limit is $200,000 for dwelling coverage and $1,000,000 for commercial property coverage</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com/general-information.html</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Underwriting restrictions</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>The FAIR Plan may decline an application or cancel a policy for properties in severe disrepair, with unsafe heating or electrical systems, or with poor maintenance; applicants with an unsatisfactory loss history may also be deemed unacceptable risks</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan - General Information</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com/general-information.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>11116 S Towne Square, Suite #303, St. Louis, MO 63123; local (314) 421-0170, toll-free (Missouri only) (800) 392-7240, fax (314) 421-2575; Monday-Friday 8:00 AM-4:00 PM</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Missouri FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Missouri Property Insurance Placement Facility (Missouri FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://missourifairplan.com</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -38306,17 +39115,35 @@
           <t>Missouri</t>
         </is>
       </c>
-      <c r="B27" s="41" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
+      <c r="B27" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="E27" s="41" t="n"/>
       <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
+      <c r="G27" s="41" t="inlineStr">
+        <is>
+          <t>UM mandatory, same limits as BI liability</t>
+        </is>
+      </c>
       <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="42" t="n"/>
+      <c r="I27" s="41" t="inlineStr">
+        <is>
+          <t>Missouri Revised Statutes 303.190 - Motor Vehicle Liability Policy, Contents</t>
+        </is>
+      </c>
+      <c r="J27" s="42" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/mo/title-xix-motor-vehicles-watercraft-and-aviation/mo-rev-st-303-190</t>
+        </is>
+      </c>
       <c r="K27" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L27" s="41" t="inlineStr">
         <is>
@@ -38325,16 +39152,16 @@
       </c>
       <c r="M27" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N27" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O27" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P27" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -50,6 +50,8 @@
     <sheet name="IN Home Verified" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="MO Auto Verified" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="MO Home Verified" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="MD Auto Verified" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="MD Home Verified" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -719,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -742,7 +744,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana and Missouri auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana and Missouri home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri and Maryland auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri and Maryland home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1870,19 +1872,19 @@
         <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C53">
+      <c r="C53" s="28">
         <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D53">
+      <c r="D53" s="28">
         <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E53">
+      <c r="E53" s="28">
         <f>COUNTIF('MO Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F53">
+      <c r="F53" s="28">
         <f>SUM(B53:E53)</f>
         <v/>
       </c>
@@ -1890,286 +1892,316 @@
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>MD Auto Verified</t>
         </is>
       </c>
       <c r="B54" s="39">
-        <f>SUM(B17:B53)</f>
+        <f>COUNTIF('MD Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C54">
-        <f>SUM(C17:C53)</f>
+      <c r="C54" s="28">
+        <f>COUNTIF('MD Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D54">
-        <f>SUM(D17:D53)</f>
+      <c r="D54" s="28">
+        <f>COUNTIF('MD Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E54">
-        <f>SUM(E17:E53)</f>
+      <c r="E54" s="28">
+        <f>COUNTIF('MD Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F54">
-        <f>SUM(F17:F53)</f>
+      <c r="F54" s="28">
+        <f>SUM(B54:E54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B55" s="39" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>MD Home Verified</t>
+        </is>
+      </c>
+      <c r="B55" s="39">
+        <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>SUM(B55:E55)</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B56" s="28" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B56" s="28">
+        <f>SUM(B17:B55)</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>SUM(C17:C55)</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>SUM(D17:D55)</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>SUM(E17:E55)</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>SUM(F17:F55)</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
@@ -2181,252 +2213,300 @@
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
-          <t>WA Home Verified</t>
+          <t>VA Home Verified</t>
         </is>
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>AZ Auto Verified</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>AZ Home Verified</t>
+          <t>WA Home Verified</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>TN Auto Verified</t>
+          <t>AZ Auto Verified</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
+          <t>AZ Home Verified</t>
+        </is>
+      </c>
+      <c r="B93" s="28" t="inlineStr">
+        <is>
+          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>TN Auto Verified</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="28" t="inlineStr">
+        <is>
           <t>TN Home Verified</t>
         </is>
       </c>
-      <c r="B93" s="28" t="inlineStr">
+      <c r="B95" s="28" t="inlineStr">
         <is>
           <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="28" t="inlineStr">
         <is>
           <t>IN Auto Verified</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B96" s="28" t="inlineStr">
         <is>
           <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>IN Home Verified</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B97" s="28" t="inlineStr">
         <is>
           <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>MO Auto Verified</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>MO Home Verified</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MD Auto Verified</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Maryland auto facts from Md. Code Transportation Section 17-103 and Insurance Sections 19-505 and 19-509, read directly from mgaleg.maryland.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MD Home Verified</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Maryland home facts from the Maryland Joint Insurance Association's (MDJIA) own website.</t>
         </is>
       </c>
     </row>
@@ -2434,11 +2514,12 @@
   <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B72:F72"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
@@ -2451,7 +2532,6 @@
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B5:F5"/>
@@ -14015,7 +14095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17364,6 +17444,106 @@
         </is>
       </c>
       <c r="E136" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Transportation Article 17-103 - Form and Minimum Benefits of Security</t>
+        </is>
+      </c>
+      <c r="B137" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C137" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gtr&amp;section=17-103&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="D137" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from mgaleg.maryland.gov.</t>
+        </is>
+      </c>
+      <c r="E137" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Insurance Article 19-505 - Personal Injury Protection Coverage, In General</t>
+        </is>
+      </c>
+      <c r="B138" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C138" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gin&amp;section=19-505&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="D138" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from mgaleg.maryland.gov.</t>
+        </is>
+      </c>
+      <c r="E138" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Insurance Article 19-509 - Uninsured Motorist Coverage, In General</t>
+        </is>
+      </c>
+      <c r="B139" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C139" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gin&amp;section=19-509&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="D139" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from mgaleg.maryland.gov.</t>
+        </is>
+      </c>
+      <c r="E139" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="B140" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C140" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="D140" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Maryland's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E140" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -33731,6 +33911,693 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Md. Code, Transportation Section 17-103(b)(1)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Transportation Article 17-103 - Form and Minimum Benefits of Security</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gtr&amp;section=17-103&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Md. Code, Transportation Section 17-103(b)(1)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Transportation Article 17-103 - Form and Minimum Benefits of Security</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gtr&amp;section=17-103&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$15,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Md. Code, Transportation Section 17-103(b)(2)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Transportation Article 17-103 - Form and Minimum Benefits of Security</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gtr&amp;section=17-103&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Personal injury protection (PIP) minimum</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>$2,500 for reasonable and necessary expenses (prosthetic devices, ambulance, dental, funeral, hospital, medical, professional nursing, surgical, and X-ray services) incurred within 3 years of the accident, plus 85% of lost income for those earning income when the accident occurred; may be waived</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Md. Code, Insurance Section 19-505</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Insurance Article 19-505 - Personal Injury Protection Coverage, In General</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gin&amp;section=19-505&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L5" s="28" t="inlineStr">
+        <is>
+          <t>Waiver governed by Insurance Section 19-506 (coverage waiver) or Section 19-506.1 (rejection).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Must at least equal the Transportation Title 17 liability minimums (30/60/15); for private passenger policies, UM coverage must equal the policy's actual liability limits unless waived</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Md. Code, Insurance Section 19-509</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Insurance Article 19-509 - Uninsured Motorist Coverage, In General</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gin&amp;section=19-509&amp;enactments=false</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Maryland FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Maryland Joint Insurance Association (MDJIA) is Maryland's FAIR Plan; every insurer licensed to write property insurance in the state is required to participate</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>MDJIA (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Maryland FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage types</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Homeowners coverage for owner-occupied single-family homes, condominiums, and town/row homes; Dwelling Property coverage for rental properties with a lease agreement; and a commercial fire program (commercial liability is not offered)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>MDJIA (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Maryland FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Exclusions</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Properties located outside Maryland and flood damage are excluded from coverage</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>MDJIA (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Maryland FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>How to apply</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Applicants should first contact a local insurance producer (agent), or may apply directly to MDJIA</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>MDJIA (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Maryland FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>3290 N Ridge Road, Suite 185, Ellicott City, MD 21043; (410) 539-6808 or 1-800-492-5670; fax (410) 244-7268; info@mdjia.org</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>MDJIA (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Maryland Joint Insurance Association (MDJIA / Maryland FAIR Plan)</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.mdjia.org/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -38881,17 +39748,39 @@
           <t>Maryland</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
+      <c r="B22" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="41" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
-      <c r="G22" s="41" t="n"/>
+      <c r="F22" s="41" t="inlineStr">
+        <is>
+          <t>PIP $2,500 minimum, waivable</t>
+        </is>
+      </c>
+      <c r="G22" s="41" t="inlineStr">
+        <is>
+          <t>UM must equal policy liability limits unless waived</t>
+        </is>
+      </c>
       <c r="H22" s="41" t="n"/>
-      <c r="I22" s="41" t="n"/>
-      <c r="J22" s="42" t="n"/>
+      <c r="I22" s="41" t="inlineStr">
+        <is>
+          <t>Maryland Transportation Article 17-103 - Form and Minimum Benefits of Security</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>https://mgaleg.maryland.gov/mgawebsite/Laws/StatuteText?article=gtr&amp;section=17-103&amp;enactments=false</t>
+        </is>
+      </c>
       <c r="K22" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L22" s="41" t="inlineStr">
         <is>
@@ -38900,16 +39789,16 @@
       </c>
       <c r="M22" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N22" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O22" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -52,6 +52,8 @@
     <sheet name="MO Home Verified" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="MD Auto Verified" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="MD Home Verified" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="WI Auto Verified" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="WI Home Verified" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -721,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -744,7 +746,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri and Maryland auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri and Maryland home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland and Wisconsin auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland and Wisconsin home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1926,19 +1928,19 @@
         <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C55">
+      <c r="C55" s="28">
         <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D55">
+      <c r="D55" s="28">
         <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E55">
+      <c r="E55" s="28">
         <f>COUNTIF('MD Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F55">
+      <c r="F55" s="28">
         <f>SUM(B55:E55)</f>
         <v/>
       </c>
@@ -1946,286 +1948,316 @@
     <row r="56">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>WI Auto Verified</t>
         </is>
       </c>
       <c r="B56" s="28">
-        <f>SUM(B17:B55)</f>
+        <f>COUNTIF('WI Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C56">
-        <f>SUM(C17:C55)</f>
+      <c r="C56" s="28">
+        <f>COUNTIF('WI Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D56">
-        <f>SUM(D17:D55)</f>
+      <c r="D56" s="28">
+        <f>COUNTIF('WI Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E56">
-        <f>SUM(E17:E55)</f>
+      <c r="E56" s="28">
+        <f>COUNTIF('WI Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F56">
-        <f>SUM(F17:F55)</f>
+      <c r="F56" s="28">
+        <f>SUM(B56:E56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B57" s="28" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>WI Home Verified</t>
+        </is>
+      </c>
+      <c r="B57" s="28">
+        <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>SUM(B57:E57)</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B58" s="28">
+        <f>SUM(B17:B57)</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>SUM(C17:C57)</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>SUM(D17:D57)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>SUM(E17:E57)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>SUM(F17:F57)</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
@@ -2237,276 +2269,324 @@
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>WA Home Verified</t>
+          <t>VA Home Verified</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>AZ Auto Verified</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>AZ Home Verified</t>
+          <t>WA Home Verified</t>
         </is>
       </c>
       <c r="B93" s="28" t="inlineStr">
         <is>
-          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>TN Auto Verified</t>
+          <t>AZ Auto Verified</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>TN Home Verified</t>
+          <t>AZ Home Verified</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
         <is>
-          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
+          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>IN Auto Verified</t>
+          <t>TN Auto Verified</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
+          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
+          <t>TN Home Verified</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>IN Auto Verified</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="inlineStr">
+        <is>
+          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
           <t>IN Home Verified</t>
         </is>
       </c>
-      <c r="B97" s="28" t="inlineStr">
+      <c r="B99" s="28" t="inlineStr">
         <is>
           <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
         <is>
           <t>MO Auto Verified</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B100" s="28" t="inlineStr">
         <is>
           <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
         <is>
           <t>MO Home Verified</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B101" s="28" t="inlineStr">
         <is>
           <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>MD Auto Verified</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Maryland auto facts from Md. Code Transportation Section 17-103 and Insurance Sections 19-505 and 19-509, read directly from mgaleg.maryland.gov.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>MD Home Verified</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Maryland home facts from the Maryland Joint Insurance Association's (MDJIA) own website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WI Auto Verified</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wisconsin auto facts from Wis. Stat. Sections 344.15, 344.62 and 632.32.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WI Home Verified</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wisconsin home facts from the Wisconsin Insurance Plan's own producer guidelines.</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2599,6 @@
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
@@ -2527,9 +2606,10 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B73:F73"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B6:F6"/>
@@ -14095,7 +14175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17544,6 +17624,106 @@
         </is>
       </c>
       <c r="E140" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.15 - Requirements as to Policy or Bond</t>
+        </is>
+      </c>
+      <c r="B141" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C141" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-15/</t>
+        </is>
+      </c>
+      <c r="D141" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator (docs.legis.wisconsin.gov timed out directly).</t>
+        </is>
+      </c>
+      <c r="E141" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.62 - Motor Vehicle Liability Insurance (Mandatory Coverage)</t>
+        </is>
+      </c>
+      <c r="B142" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C142" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-62.html</t>
+        </is>
+      </c>
+      <c r="D142" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E142" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 632.32 - Provisions of Motor Vehicle Insurance Policies</t>
+        </is>
+      </c>
+      <c r="B143" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C143" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/insurance-ch-600-to-655/wi-st-632-32/</t>
+        </is>
+      </c>
+      <c r="D143" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E143" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="B144" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C144" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="D144" s="28" t="inlineStr">
+        <is>
+          <t>Official 25-page producer guidelines PDF, published by the plan's own administrator and overseen by the Wisconsin OCI.</t>
+        </is>
+      </c>
+      <c r="E144" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -34598,6 +34778,794 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 344.15(1)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.15 - Requirements as to Policy or Bond</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-15/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 344.15(1)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.15 - Requirements as to Policy or Bond</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-15/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 344.15(1)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.15 - Requirements as to Policy or Bond</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-15/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Mandatory liability insurance and proof of insurance</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>No person may operate a vehicle on Wisconsin highways without an active motor vehicle liability policy; operators must carry proof of compliance and display it on request, in printed or electronic format including on a cellular phone, and officers may not view other phone content while checking digital proof</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 344.62</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.62 - Motor Vehicle Liability Insurance (Mandatory Coverage)</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-62.html</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured and underinsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist (UM) coverage is mandatory at a minimum of $25,000 per person and $50,000 per accident; underinsured motorist (UIM) coverage is optional (absence of a premium payment for it is conclusive proof of rejection after notice) but if accepted must be at least $50,000 per person and $100,000 per accident</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 632.32</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 632.32 - Provisions of Motor Vehicle Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/insurance-ch-600-to-655/wi-st-632-32/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Medical payments coverage</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Required at a minimum of $1,000 per person, though policyholders may reject this coverage in writing</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>Wis. Stat. Section 632.32</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 632.32 - Provisions of Motor Vehicle Insurance Policies</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/insurance-ch-600-to-655/wi-st-632-32/</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Wisconsin Insurance Plan (WIP) is Wisconsin's FAIR Plan / residual property insurer, created to provide basic property insurance on properties rejected for coverage by other insurers; it is composed of all insurance companies authorized to write property insurance in Wisconsin, operates under Wisconsin Administrative Code Ins 4.10, and is supervised by the Commissioner of Insurance</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Homeowner Program coverage structure</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>A single Dwelling limit from $15,000 to $350,000 is selected; Other Structures (10% of Dwelling), Personal Property (50% of Dwelling), and Additional Living Expense (10% of Dwelling) are set as a fixed package; Personal Liability is a fixed $100,000 and Medical Payments to Others a fixed $1,000 (neither can be changed); on-premises-only theft coverage starts at $1,000 and can be increased in $1,000 increments up to $5,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Homeowner/Dwelling deductibles</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum deductible is $250 for a dwelling limit up to $75,000, $500 up to $150,000, and $1,000 up to $250,000; a $2,500 deductible is also available</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Settlement basis (Actual Cash Value)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>WIP policies pay Actual Cash Value, not replacement cost; the maximum coverage offered is based on the property's most recent tax-assessed fair market value for land improvements plus $40,000 (Homeowner/Dwelling Fire) or $50,000 (Commercial Fire), rounded up</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Ineligible properties</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>The Plan cannot insure motor vehicles, manufacturing properties, or farms with annual gross sales over $5,000</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Cancellation and non-renewal notice periods</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>13 days' notice for nonpayment of premium, for a policy within its first 60 days, or for mid-term cancellation due to material misrepresentation or a substantial change in risk; 60 days' notice is required for non-renewal</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>WIP Producer Guidelines (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin Insurance Plan (WIP / Wisconsin Property Insurance Association) - Producer Guidelines</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>https://www.wisinsplan.com/wp-content/uploads/2025/01/UnderwritingGuidelines-online-revised-1.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -41250,17 +42218,39 @@
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B51" s="41" t="n"/>
-      <c r="C51" s="41" t="n"/>
-      <c r="D51" s="41" t="n"/>
+      <c r="B51" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C51" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D51" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E51" s="41" t="n"/>
-      <c r="F51" s="41" t="n"/>
-      <c r="G51" s="41" t="n"/>
+      <c r="F51" s="41" t="inlineStr">
+        <is>
+          <t>Med pay $1,000 min, rejectable</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
+        <is>
+          <t>UM mandatory 25/50; UIM optional, at least 50/100 if accepted</t>
+        </is>
+      </c>
       <c r="H51" s="41" t="n"/>
-      <c r="I51" s="41" t="n"/>
-      <c r="J51" s="42" t="n"/>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>Wisconsin Statute 344.15 - Requirements as to Policy or Bond</t>
+        </is>
+      </c>
+      <c r="J51" s="42" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/wi/vehicles-ch-340-to-351/wi-st-344-15/</t>
+        </is>
+      </c>
       <c r="K51" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L51" s="41" t="inlineStr">
         <is>
@@ -41269,16 +42259,16 @@
       </c>
       <c r="M51" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N51" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O51" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P51" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -54,6 +54,8 @@
     <sheet name="MD Home Verified" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="WI Auto Verified" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="WI Home Verified" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="CO Auto Verified" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="CO Home Verified" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -723,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -746,7 +748,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland and Wisconsin auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland and Wisconsin home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin and Colorado auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin and Colorado home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -1982,19 +1984,19 @@
         <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C57">
+      <c r="C57" s="28">
         <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D57">
+      <c r="D57" s="28">
         <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E57">
+      <c r="E57" s="28">
         <f>COUNTIF('WI Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F57">
+      <c r="F57" s="28">
         <f>SUM(B57:E57)</f>
         <v/>
       </c>
@@ -2002,286 +2004,316 @@
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>CO Auto Verified</t>
         </is>
       </c>
       <c r="B58" s="28">
-        <f>SUM(B17:B57)</f>
+        <f>COUNTIF('CO Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C58">
-        <f>SUM(C17:C57)</f>
+      <c r="C58" s="28">
+        <f>COUNTIF('CO Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D58">
-        <f>SUM(D17:D57)</f>
+      <c r="D58" s="28">
+        <f>COUNTIF('CO Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E58">
-        <f>SUM(E17:E57)</f>
+      <c r="E58" s="28">
+        <f>COUNTIF('CO Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F58">
-        <f>SUM(F17:F57)</f>
+      <c r="F58" s="28">
+        <f>SUM(B58:E58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B59" s="28" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>CO Home Verified</t>
+        </is>
+      </c>
+      <c r="B59" s="28">
+        <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>SUM(B59:E59)</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B60" s="28">
+        <f>SUM(B17:B59)</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>SUM(C17:C59)</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>SUM(D17:D59)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>SUM(E17:E59)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>SUM(F17:F59)</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
@@ -2293,316 +2325,363 @@
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>WA Home Verified</t>
+          <t>VA Home Verified</t>
         </is>
       </c>
       <c r="B93" s="28" t="inlineStr">
         <is>
-          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>AZ Auto Verified</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>AZ Home Verified</t>
+          <t>WA Home Verified</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
         <is>
-          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>TN Auto Verified</t>
+          <t>AZ Auto Verified</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>TN Home Verified</t>
+          <t>AZ Home Verified</t>
         </is>
       </c>
       <c r="B97" s="28" t="inlineStr">
         <is>
-          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
+          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
-          <t>IN Auto Verified</t>
+          <t>TN Auto Verified</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
+          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="28" t="inlineStr">
         <is>
-          <t>IN Home Verified</t>
+          <t>TN Home Verified</t>
         </is>
       </c>
       <c r="B99" s="28" t="inlineStr">
         <is>
-          <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
+          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="28" t="inlineStr">
         <is>
-          <t>MO Auto Verified</t>
+          <t>IN Auto Verified</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
+          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
+          <t>IN Home Verified</t>
+        </is>
+      </c>
+      <c r="B101" s="28" t="inlineStr">
+        <is>
+          <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>MO Auto Verified</t>
+        </is>
+      </c>
+      <c r="B102" s="28" t="inlineStr">
+        <is>
+          <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
           <t>MO Home Verified</t>
         </is>
       </c>
-      <c r="B101" s="28" t="inlineStr">
+      <c r="B103" s="28" t="inlineStr">
         <is>
           <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
         <is>
           <t>MD Auto Verified</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B104" s="28" t="inlineStr">
         <is>
           <t>Maryland auto facts from Md. Code Transportation Section 17-103 and Insurance Sections 19-505 and 19-509, read directly from mgaleg.maryland.gov.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="28" t="inlineStr">
         <is>
           <t>MD Home Verified</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B105" s="28" t="inlineStr">
         <is>
           <t>Maryland home facts from the Maryland Joint Insurance Association's (MDJIA) own website.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>WI Auto Verified</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Wisconsin auto facts from Wis. Stat. Sections 344.15, 344.62 and 632.32.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>WI Home Verified</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Wisconsin home facts from the Wisconsin Insurance Plan's own producer guidelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CO Auto Verified</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Colorado auto facts from Colo. Rev. Stat. Sections 10-4-620, 10-4-621 and 10-4-609.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CO Home Verified</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Colorado home facts from the Colorado FAIR Plan's own site and a DORA advisory bulletin.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B75:F75"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B59:F59"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B60:F60"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
@@ -2615,6 +2694,7 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -14175,7 +14255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17724,6 +17804,131 @@
         </is>
       </c>
       <c r="E144" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-620 - Required Coverage</t>
+        </is>
+      </c>
+      <c r="B145" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C145" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-620/</t>
+        </is>
+      </c>
+      <c r="D145" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E145" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-621 - Required Coverages Are Minimum</t>
+        </is>
+      </c>
+      <c r="B146" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C146" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-621/</t>
+        </is>
+      </c>
+      <c r="D146" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E146" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-609 - Insurance Protection Against Uninsured Motorists</t>
+        </is>
+      </c>
+      <c r="B147" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C147" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-609/</t>
+        </is>
+      </c>
+      <c r="D147" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read via a legal-code aggregator.</t>
+        </is>
+      </c>
+      <c r="E147" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan - About</t>
+        </is>
+      </c>
+      <c r="B148" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C148" s="28" t="inlineStr">
+        <is>
+          <t>https://www.coloradofairplan.com/about</t>
+        </is>
+      </c>
+      <c r="D148" s="28" t="inlineStr">
+        <is>
+          <t>Official site of the plan's own administrator (Colorado's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E148" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA - FAIR Plan Advisory Bulletin</t>
+        </is>
+      </c>
+      <c r="B149" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C149" s="28" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/CODORA/bulletins/3d22387</t>
+        </is>
+      </c>
+      <c r="D149" s="28" t="inlineStr">
+        <is>
+          <t>Official advisory bulletin from the Colorado Division of Insurance (DORA).</t>
+        </is>
+      </c>
+      <c r="E149" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -35566,6 +35771,688 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Colo. Rev. Stat. Section 10-4-620</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-620 - Required Coverage</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-620/</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Colo. Rev. Stat. Section 10-4-620</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-620 - Required Coverage</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-620/</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$15,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Colo. Rev. Stat. Section 10-4-620</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-620 - Required Coverage</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-620/</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Minimums are a floor, not a ceiling</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Nothing in Colorado's compulsory-insurance law prohibits an insurer from issuing policies with coverage more extensive than the statutory minimum</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Colo. Rev. Stat. Section 10-4-621</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-621 - Required Coverages Are Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-621/</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Insurers must offer uninsured motorist (UM) coverage at an amount equal to the insured's bodily injury liability limits (never required to offer more); the named insured may reject the coverage in writing, except that a transportation network company's own policy may not reject UM coverage for periods when its driver is engaged in a prearranged ride</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Colo. Rev. Stat. Section 10-4-609</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-609 - Insurance Protection Against Uninsured Motorists</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-609/</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Colorado FAIR Plan is a stand-alone not-for-profit organization, signed into law in 2023, serving as the state's property insurer of last resort; it is funded by assessments on admitted insurance carriers writing property coverage in Colorado, not public dollars</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan - About</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.coloradofairplan.com/about</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Applicants must own property deemed uninsurable by the standard market (due to factors such as wildfire or hail risk, claims history, age, or location), obtain three declinations from standard insurers, and work with a licensed, registered agent to confirm eligibility and apply</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan - About</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.coloradofairplan.com/about</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage limits</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Homeowners/residential coverage is capped at a combined $750,000 for property and contents, settled at Actual Cash Value (not replacement cost); commercial property coverage is capped at a combined $5,000,000, also on an Actual Cash Value basis</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA FAIR Plan advisory bulletin</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA - FAIR Plan Advisory Bulletin</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/CODORA/bulletins/3d22387</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Covered perils</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Fire or lightning, windstorm or hail, explosion, riot or civil commotion, aircraft, vehicles, smoke, volcanic eruption, and vandalism or malicious mischief</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA FAIR Plan advisory bulletin</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA - FAIR Plan Advisory Bulletin</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/CODORA/bulletins/3d22387</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Key exclusions</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Earthquake and flood damage are not among the covered perils; this is a limited-perils plan that may not adequately serve all property types, including larger associations</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA FAIR Plan advisory bulletin</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado DORA - FAIR Plan Advisory Bulletin</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/CODORA/bulletins/3d22387</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -39920,17 +40807,35 @@
           <t>Colorado</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
+      <c r="B7" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="E7" s="41" t="n"/>
       <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>UM offered at policy BI limits, rejectable</t>
+        </is>
+      </c>
       <c r="H7" s="41" t="n"/>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="42" t="n"/>
+      <c r="I7" s="41" t="inlineStr">
+        <is>
+          <t>Colorado Revised Statutes 10-4-620 - Required Coverage</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
+        <is>
+          <t>https://codes.findlaw.com/co/title-10-insurance/co-rev-st-sect-10-4-620/</t>
+        </is>
+      </c>
       <c r="K7" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L7" s="41" t="inlineStr">
         <is>
@@ -39939,16 +40844,16 @@
       </c>
       <c r="M7" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N7" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O7" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P7" s="41" t="inlineStr">
         <is>

--- a/DATA/Insurance_Reference_Data_v5.xlsx
+++ b/DATA/Insurance_Reference_Data_v5.xlsx
@@ -56,6 +56,8 @@
     <sheet name="WI Home Verified" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="CO Auto Verified" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="CO Home Verified" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="MN Auto Verified" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="MN Home Verified" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CA Auto Verified'!$A$1:$L$32</definedName>
@@ -725,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -748,7 +750,7 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin and Colorado auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin and Colorado home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
+          <t>Structured reference data from research through October 1, 2026 (California auto and home; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin, Colorado and Minnesota auto; Texas, Florida, New York, Illinois, Pennsylvania, Georgia, North Carolina, New Jersey, Virginia, Washington, Arizona, Tennessee, Indiana, Missouri, Maryland, Wisconsin, Colorado and Minnesota home verified from primary sources; California home credit-use rules still open) for the U.S. auto and home insurance education/comparison project.</t>
         </is>
       </c>
     </row>
@@ -2038,19 +2040,19 @@
         <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C59">
+      <c r="C59" s="28">
         <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D59">
+      <c r="D59" s="28">
         <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E59">
+      <c r="E59" s="28">
         <f>COUNTIF('CO Home Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F59">
+      <c r="F59" s="28">
         <f>SUM(B59:E59)</f>
         <v/>
       </c>
@@ -2058,286 +2060,316 @@
     <row r="60">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>All tabs</t>
+          <t>MN Auto Verified</t>
         </is>
       </c>
       <c r="B60" s="28">
-        <f>SUM(B17:B59)</f>
+        <f>COUNTIF('MN Auto Verified'!$J$2:$J$500,"Primary source")</f>
         <v/>
       </c>
-      <c r="C60">
-        <f>SUM(C17:C59)</f>
+      <c r="C60" s="28">
+        <f>COUNTIF('MN Auto Verified'!$J$2:$J$500,"Secondary - unverified")</f>
         <v/>
       </c>
-      <c r="D60">
-        <f>SUM(D17:D59)</f>
+      <c r="D60" s="28">
+        <f>COUNTIF('MN Auto Verified'!$J$2:$J$500,"Conflicting")</f>
         <v/>
       </c>
-      <c r="E60">
-        <f>SUM(E17:E59)</f>
+      <c r="E60" s="28">
+        <f>COUNTIF('MN Auto Verified'!$J$2:$J$500,"Not researched")</f>
         <v/>
       </c>
-      <c r="F60">
-        <f>SUM(F17:F59)</f>
+      <c r="F60" s="28">
+        <f>SUM(B60:E60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>TX Home Verified</t>
-        </is>
-      </c>
-      <c r="B61" s="28" t="inlineStr">
-        <is>
-          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
-        </is>
+          <t>MN Home Verified</t>
+        </is>
+      </c>
+      <c r="B61" s="28">
+        <f>COUNTIF('MN Home Verified'!$J$2:$J$500,"Primary source")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>COUNTIF('MN Home Verified'!$J$2:$J$500,"Secondary - unverified")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>COUNTIF('MN Home Verified'!$J$2:$J$500,"Conflicting")</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>COUNTIF('MN Home Verified'!$J$2:$J$500,"Not researched")</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>SUM(B61:E61)</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
         <is>
-          <t>FL Home Verified</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="inlineStr">
-        <is>
-          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
-        </is>
+          <t>All tabs</t>
+        </is>
+      </c>
+      <c r="B62" s="28">
+        <f>SUM(B17:B61)</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>SUM(C17:C61)</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>SUM(D17:D61)</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>SUM(E17:E61)</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>SUM(F17:F61)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t>TX Auto Verified</t>
+          <t>TX Home Verified</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Texas auto facts from the TDI guide.</t>
+          <t>Texas home facts from TDI, TWIA and secondary sources.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="28" t="inlineStr">
         <is>
-          <t>FL Auto Verified</t>
+          <t>FL Home Verified</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
+          <t>Florida home facts: hurricane deductibles, Citizens and flood rules.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="28" t="inlineStr">
         <is>
-          <t>NY Auto Verified</t>
+          <t>TX Auto Verified</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>New York auto facts from the DFS consumer guide.</t>
+          <t>Texas auto facts from the TDI guide.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
         <is>
-          <t>CA Home Verified</t>
+          <t>FL Auto Verified</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
+          <t>Florida auto facts from FLHSMV and Florida Statutes.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>CA Auto Verified</t>
+          <t>NY Auto Verified</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
+          <t>New York auto facts from the DFS consumer guide.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
         <is>
-          <t>State Min Limits</t>
+          <t>CA Home Verified</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
+          <t>California home insurance facts traced to CDI, CEA and FAIR Plan sources and CDI press releases.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Rating Factors</t>
+          <t>CA Auto Verified</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Credit, gender and age rules by state for states researched.</t>
+          <t>California auto facts traced to primary sources (CDI, DMV, statutes and regulations).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>Discounts</t>
+          <t>State Min Limits</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Discount availability by state and carrier.</t>
+          <t>Minimum auto liability limits by state (50 states + DC); most rows still to research.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>Telematics</t>
+          <t>Rating Factors</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Usage-based programs by carrier.</t>
+          <t>Credit, gender and age rules by state for states researched.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>Coverage Details</t>
+          <t>Discounts</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Flood, earthquake, umbrella and other coverage facts.</t>
+          <t>Discount availability by state and carrier.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>Price Benchmarks</t>
+          <t>Telematics</t>
         </is>
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>Published average premiums with spread formulas.</t>
+          <t>Usage-based programs by carrier.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>Regulatory Watch</t>
+          <t>Coverage Details</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Laws and rules to monitor.</t>
+          <t>Flood, earthquake, umbrella and other coverage facts.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>Quote Source Options</t>
+          <t>Price Benchmarks</t>
         </is>
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>Ways to get real quotes and what each implies.</t>
+          <t>Published average premiums with spread formulas.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>Legal Review Checklist</t>
+          <t>Regulatory Watch</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Questions to bring to insurance-regulatory counsel.</t>
+          <t>Laws and rules to monitor.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>Refresh Schedule</t>
+          <t>Quote Source Options</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>Owners, review intervals and overdue checks (formulas).</t>
+          <t>Ways to get real quotes and what each implies.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>Conflicts Log</t>
+          <t>Legal Review Checklist</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Where sources disagree and what to verify.</t>
+          <t>Questions to bring to insurance-regulatory counsel.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Refresh Schedule</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>Every source used, with type and reliability note.</t>
+          <t>Owners, review intervals and overdue checks (formulas).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>Tabs (additional entries below)</t>
+          <t>Conflicts Log</t>
         </is>
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
+          <t>Where sources disagree and what to verify.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>NY Home Verified</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
+          <t>Every source used, with type and reliability note.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>IL Auto Verified</t>
+          <t>Tabs (additional entries below)</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
@@ -2349,324 +2381,372 @@
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>IL Home Verified</t>
+          <t>NY Home Verified</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
+          <t>New York home facts from the DFS homeowners guide, NYPIUA, and the cancellations/non-renewals and discounts pages.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>PA Auto Verified</t>
+          <t>IL Auto Verified</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
+          <t>Illinois auto facts from the IDOI shopping guide and the Illinois credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>PA Home Verified</t>
+          <t>IL Home Verified</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
+          <t>Illinois home facts from the IDOI homeowner guide, the Illinois FAIR Plan, non-renewal rules, and the credit-scoring statute.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>GA Auto Verified</t>
+          <t>PA Auto Verified</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
+          <t>Pennsylvania auto facts from the official IDOI Automobile Insurance Guide.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>GA Home Verified</t>
+          <t>PA Home Verified</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
+          <t>Pennsylvania home facts from the official IDOI Homeowners Insurance Guide and the PA FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>NC Auto Verified</t>
+          <t>GA Auto Verified</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
+          <t>Georgia auto facts from the official OCI Consumer Guide for Automobile Insurance.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="28" t="inlineStr">
         <is>
-          <t>NC Home Verified</t>
+          <t>GA Home Verified</t>
         </is>
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
+          <t>Georgia home facts from the official OCI Consumer Guide for Homeowners Insurance and the Georgia FAIR Plan.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>NJ Auto Verified</t>
+          <t>NC Auto Verified</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
+          <t>North Carolina auto facts from NCDOI and the NC DMV.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
         <is>
-          <t>NJ Home Verified</t>
+          <t>NC Home Verified</t>
         </is>
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
+          <t>North Carolina home facts from the NCJUA/NCIUA FAIR and Beach Plans.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>VA Auto Verified</t>
+          <t>NJ Auto Verified</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
+          <t>New Jersey auto facts from the NJDOBI bulletin on 2026 minimum-limit increases and the verbatim AICRA statute (N.J.S.A. 39:6A-3.1) for the Basic Policy.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>VA Home Verified</t>
+          <t>NJ Home Verified</t>
         </is>
       </c>
       <c r="B93" s="28" t="inlineStr">
         <is>
-          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
+          <t>New Jersey home facts from the official NJDOBI consumer guide and the NJIUA (FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>WA Auto Verified</t>
+          <t>VA Auto Verified</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
+          <t>Virginia auto facts from the official VA DMV insurance-requirements page.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="28" t="inlineStr">
         <is>
-          <t>WA Home Verified</t>
+          <t>VA Home Verified</t>
         </is>
       </c>
       <c r="B95" s="28" t="inlineStr">
         <is>
-          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
+          <t>Virginia home facts from the Virginia Property Insurance Association (VPIA / FAIR Plan).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>AZ Auto Verified</t>
+          <t>WA Auto Verified</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
+          <t>Washington auto facts from the official WA OIC mandatory insurance law page.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>AZ Home Verified</t>
+          <t>WA Home Verified</t>
         </is>
       </c>
       <c r="B97" s="28" t="inlineStr">
         <is>
-          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
+          <t>Washington home facts from the Washington FAIR Plan's own FAQ page.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
-          <t>TN Auto Verified</t>
+          <t>AZ Auto Verified</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
+          <t>Arizona auto facts from A.R.S. Sections 28-4009 and 28-4135, read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="28" t="inlineStr">
         <is>
-          <t>TN Home Verified</t>
+          <t>AZ Home Verified</t>
         </is>
       </c>
       <c r="B99" s="28" t="inlineStr">
         <is>
-          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
+          <t>Arizona home facts from A.R.S. Sections 20-2202 and 20-1652 (no state FAIR Plan; cancellation/nonrenewal rules), read directly from azleg.gov.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="28" t="inlineStr">
         <is>
-          <t>IN Auto Verified</t>
+          <t>TN Auto Verified</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
+          <t>Tennessee auto facts from Tenn. Code Ann. Sections 55-12-102, 56-7-1303 and 56-7-1304.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>IN Home Verified</t>
+          <t>TN Home Verified</t>
         </is>
       </c>
       <c r="B101" s="28" t="inlineStr">
         <is>
-          <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
+          <t>Tennessee home facts: no state FAIR Plan (per NAIC), plus Tenn. Code Ann. Sections 56-7-113 and 56-7-114.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="28" t="inlineStr">
         <is>
-          <t>MO Auto Verified</t>
+          <t>IN Auto Verified</t>
         </is>
       </c>
       <c r="B102" s="28" t="inlineStr">
         <is>
-          <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
+          <t>Indiana auto facts from Indiana Code Sections 9-25-4-5 and 27-7-5-2.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="28" t="inlineStr">
         <is>
-          <t>MO Home Verified</t>
+          <t>IN Home Verified</t>
         </is>
       </c>
       <c r="B103" s="28" t="inlineStr">
         <is>
-          <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
+          <t>Indiana home facts from the Indiana FAIR Plan's own website.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="28" t="inlineStr">
         <is>
-          <t>MD Auto Verified</t>
+          <t>MO Auto Verified</t>
         </is>
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>Maryland auto facts from Md. Code Transportation Section 17-103 and Insurance Sections 19-505 and 19-509, read directly from mgaleg.maryland.gov.</t>
+          <t>Missouri auto facts from Missouri Revised Statutes Sections 303.190 and 379.203.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="28" t="inlineStr">
         <is>
+          <t>MO Home Verified</t>
+        </is>
+      </c>
+      <c r="B105" s="28" t="inlineStr">
+        <is>
+          <t>Missouri home facts from the Missouri FAIR Plan's own website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>MD Auto Verified</t>
+        </is>
+      </c>
+      <c r="B106" s="28" t="inlineStr">
+        <is>
+          <t>Maryland auto facts from Md. Code Transportation Section 17-103 and Insurance Sections 19-505 and 19-509, read directly from mgaleg.maryland.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
           <t>MD Home Verified</t>
         </is>
       </c>
-      <c r="B105" s="28" t="inlineStr">
+      <c r="B107" s="28" t="inlineStr">
         <is>
           <t>Maryland home facts from the Maryland Joint Insurance Association's (MDJIA) own website.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="28" t="inlineStr">
         <is>
           <t>WI Auto Verified</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B108" s="28" t="inlineStr">
         <is>
           <t>Wisconsin auto facts from Wis. Stat. Sections 344.15, 344.62 and 632.32.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="28" t="inlineStr">
         <is>
           <t>WI Home Verified</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B109" s="28" t="inlineStr">
         <is>
           <t>Wisconsin home facts from the Wisconsin Insurance Plan's own producer guidelines.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>CO Auto Verified</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Colorado auto facts from Colo. Rev. Stat. Sections 10-4-620, 10-4-621 and 10-4-609.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>CO Home Verified</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Colorado home facts from the Colorado FAIR Plan's own site and a DORA advisory bulletin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MN Auto Verified</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Minnesota auto facts from Minn. Stat. Sections 65B.49 and 65B.44, read directly from revisor.mn.gov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MN Home Verified</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Minnesota home facts from the Minnesota FAIR Plan's own consumer brochure.</t>
         </is>
       </c>
     </row>
@@ -2674,19 +2754,19 @@
   <mergeCells count="24">
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
@@ -14255,7 +14335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="58" customWidth="1" style="28" min="1" max="1"/>
@@ -17929,6 +18009,81 @@
         </is>
       </c>
       <c r="E149" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="B150" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C150" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
+      <c r="D150" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from revisor.mn.gov.</t>
+        </is>
+      </c>
+      <c r="E150" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.44 - Basic Economic Loss Benefits</t>
+        </is>
+      </c>
+      <c r="B151" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C151" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.44</t>
+        </is>
+      </c>
+      <c r="D151" s="28" t="inlineStr">
+        <is>
+          <t>Verbatim statute text, read directly from revisor.mn.gov.</t>
+        </is>
+      </c>
+      <c r="E151" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="B152" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="D152" s="28" t="inlineStr">
+        <is>
+          <t>Official consumer brochure published by the plan's own administrator (Minnesota's FAIR Plan).</t>
+        </is>
+      </c>
+      <c r="E152" s="48" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -37301,6 +37456,693 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per person</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Minn. Stat. Section 65B.49</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Bodily injury per accident</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Minn. Stat. Section 65B.49</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minimum liability</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Property damage</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Minn. Stat. Section 65B.49</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Personal injury protection (Basic Economic Loss Benefits)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Minimum $40,000 per person, split into $20,000 for medical expense loss and a combined $20,000 for income loss, replacement services, funeral expense, and survivors' benefits; income-loss and survivors'-economic-loss benefits are capped at $500/week, replacement-services benefits at $200/week, and funeral/burial expenses at $5,000</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Minn. Stat. Section 65B.44</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.44 - Basic Economic Loss Benefits</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.44</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota is a mandatory no-fault state under the Minnesota No-Fault Automobile Insurance Act (Minn. Stat. ch. 65B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Uninsured and underinsured motorist coverage</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Mandatory and must be provided as separate coverages on every policy, at a minimum of $25,000 per person and $50,000 per accident</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Minn. Stat. Section 65B.49, subd. 3a</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Fact</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Legal Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Date Collected</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Geographic Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>The Minnesota FAIR Plan was created by an act of the Minnesota Legislature to provide limited property insurance when coverage is not available from the private market, to encourage improvement of insured properties, and to help customers return to the private market</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan consumer brochure (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K2" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Settlement basis</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Coverage is Non-Replacement, based on the market value of the insured property, for a limited number of causes of loss - unlike private insurers, which provide Replacement Cost coverage for more causes of loss</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan consumer brochure (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K3" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Coverage types offered</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Dwellings (fire, extended coverage, and vandalism; no theft) for owner-occupied, non-owner-occupied, vacant, or seasonal properties; Homeowners (includes theft and liability) for owner-occupied, condominium unit owners, or renters' contents; Commercial Properties; Farms (includes theft); and Cooperative Housing</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan consumer brochure (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>How to apply</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Apply through any licensed insurance agent, who is required to help any applicant seeking FAIR Plan coverage; the application must include photos of the structures and documentation of market value (recent property tax information or sale documentation); a field inspection may be required at no cost to the applicant</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan consumer brochure (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>1128 Harmon Pl, Suite 311, Minneapolis, MN 55403-2041; 612-338-7584 or 800-524-1640; fax 612-338-4543; www.mnfairplan.org</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan consumer brochure (plan administrator)</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota FAIR Plan - Consumer Brochure</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>https://mnfairplan.org/assets/pdfs/policy-forms/other-docs/brochure09-22-14.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Regulator-published</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -41793,17 +42635,43 @@
           <t>Minnesota</t>
         </is>
       </c>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="41" t="n"/>
-      <c r="D25" s="41" t="n"/>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="41" t="n"/>
-      <c r="G25" s="41" t="n"/>
+      <c r="B25" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="C25" s="41" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>No-fault (mandatory PIP)</t>
+        </is>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>PIP (Basic Economic Loss) $40,000 min per person</t>
+        </is>
+      </c>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>UM/UIM mandatory, separate coverages, $25,000/$50,000 min</t>
+        </is>
+      </c>
       <c r="H25" s="41" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="42" t="n"/>
+      <c r="I25" s="41" t="inlineStr">
+        <is>
+          <t>Minnesota Statute 65B.49 - Minimum Security Requirements</t>
+        </is>
+      </c>
+      <c r="J25" s="42" t="inlineStr">
+        <is>
+          <t>https://www.revisor.mn.gov/statutes/cite/65B.49</t>
+        </is>
+      </c>
       <c r="K25" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L25" s="41" t="inlineStr">
         <is>
@@ -41812,16 +42680,16 @@
       </c>
       <c r="M25" s="41" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Regulator-published</t>
         </is>
       </c>
       <c r="N25" s="47" t="inlineStr">
         <is>
-          <t>Not researched</t>
+          <t>Primary source</t>
         </is>
       </c>
       <c r="O25" s="43" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="P25" s="41" t="inlineStr">
         <is>
